--- a/research/traditional_assets/database/data/croatia/croatia_computer_services.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_computer_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1046495614071652</v>
+        <v>0.1044980921966323</v>
       </c>
       <c r="C2">
-        <v>96.50306368326949</v>
+        <v>95.74517431464989</v>
       </c>
       <c r="D2">
-        <v>80.80306368326949</v>
+        <v>81.01157431464988</v>
       </c>
       <c r="E2">
-        <v>-7.339999999999999</v>
+        <v>-6.373599999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9664</v>
       </c>
       <c r="G2">
         <v>15.7</v>
@@ -1439,28 +1439,28 @@
         <v>1.87</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04860992</v>
       </c>
       <c r="N2">
-        <v>1.87</v>
+        <v>1.82139008</v>
       </c>
       <c r="O2">
-        <v>0.3366</v>
+        <v>0.3278502144</v>
       </c>
       <c r="P2">
-        <v>1.5334</v>
+        <v>1.4935398656</v>
       </c>
       <c r="Q2">
-        <v>6.063400000000001</v>
+        <v>6.0235398656</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1046495614071652</v>
+        <v>0.1051370022188205</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>1.000507102228907</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>38.46951404157834</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1044980921966323</v>
+        <v>0.1043466229860994</v>
       </c>
       <c r="C3">
-        <v>95.74517431464989</v>
+        <v>94.98836384483305</v>
       </c>
       <c r="D3">
-        <v>81.01157431464988</v>
+        <v>81.22116384483304</v>
       </c>
       <c r="E3">
-        <v>-6.373599999999999</v>
+        <v>-5.407199999999999</v>
       </c>
       <c r="F3">
-        <v>0.9664</v>
+        <v>1.9328</v>
       </c>
       <c r="G3">
         <v>15.7</v>
@@ -1521,28 +1521,28 @@
         <v>1.87</v>
       </c>
       <c r="M3">
-        <v>0.04860992</v>
+        <v>0.09721984</v>
       </c>
       <c r="N3">
-        <v>1.82139008</v>
+        <v>1.77278016</v>
       </c>
       <c r="O3">
-        <v>0.3278502144</v>
+        <v>0.3191004288</v>
       </c>
       <c r="P3">
-        <v>1.4935398656</v>
+        <v>1.4536797312</v>
       </c>
       <c r="Q3">
-        <v>6.0235398656</v>
+        <v>5.983679731200001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1051370022188205</v>
+        <v>0.1056343908021422</v>
       </c>
       <c r="T3">
-        <v>1.000507102228907</v>
+        <v>1.008893788302899</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>38.46951404157834</v>
+        <v>19.23475702078917</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1043466229860994</v>
+        <v>0.1042320537755665</v>
       </c>
       <c r="C4">
-        <v>94.98836384483305</v>
+        <v>94.18121624174528</v>
       </c>
       <c r="D4">
-        <v>81.22116384483304</v>
+        <v>81.38041624174527</v>
       </c>
       <c r="E4">
-        <v>-5.407199999999999</v>
+        <v>-4.440799999999999</v>
       </c>
       <c r="F4">
-        <v>1.9328</v>
+        <v>2.8992</v>
       </c>
       <c r="G4">
         <v>15.7</v>
@@ -1603,45 +1603,45 @@
         <v>1.87</v>
       </c>
       <c r="M4">
-        <v>0.09721984</v>
+        <v>0.15017856</v>
       </c>
       <c r="N4">
-        <v>1.77278016</v>
+        <v>1.71982144</v>
       </c>
       <c r="O4">
-        <v>0.3191004288</v>
+        <v>0.3095678592</v>
       </c>
       <c r="P4">
-        <v>1.4536797312</v>
+        <v>1.4102535808</v>
       </c>
       <c r="Q4">
-        <v>5.983679731200001</v>
+        <v>5.9402535808</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1056343908021422</v>
+        <v>0.1061420348201716</v>
       </c>
       <c r="T4">
-        <v>1.008893788302899</v>
+        <v>1.01745339573924</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.18</v>
       </c>
       <c r="W4">
-        <v>0.041246</v>
+        <v>0.042476</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>19.23475702078917</v>
+        <v>12.45184399157909</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1042320537755665</v>
+        <v>0.1041486445650336</v>
       </c>
       <c r="C5">
-        <v>94.18121624174528</v>
+        <v>93.33114930007363</v>
       </c>
       <c r="D5">
-        <v>81.38041624174527</v>
+        <v>81.49674930007363</v>
       </c>
       <c r="E5">
-        <v>-4.440799999999999</v>
+        <v>-3.474399999999999</v>
       </c>
       <c r="F5">
-        <v>2.8992</v>
+        <v>3.8656</v>
       </c>
       <c r="G5">
         <v>15.7</v>
@@ -1685,45 +1685,45 @@
         <v>1.87</v>
       </c>
       <c r="M5">
-        <v>0.15017856</v>
+        <v>0.2068096</v>
       </c>
       <c r="N5">
-        <v>1.71982144</v>
+        <v>1.6631904</v>
       </c>
       <c r="O5">
-        <v>0.3095678592</v>
+        <v>0.299374272</v>
       </c>
       <c r="P5">
-        <v>1.4102535808</v>
+        <v>1.363816128</v>
       </c>
       <c r="Q5">
-        <v>5.9402535808</v>
+        <v>5.893816128000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1061420348201716</v>
+        <v>0.1066602547552433</v>
       </c>
       <c r="T5">
-        <v>1.01745339573924</v>
+        <v>1.026191328330506</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.18</v>
       </c>
       <c r="W5">
-        <v>0.042476</v>
+        <v>0.04387</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>12.45184399157909</v>
+        <v>9.042133440613975</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1041486445650336</v>
+        <v>0.1040562153545007</v>
       </c>
       <c r="C6">
-        <v>93.33114930007363</v>
+        <v>92.49405190157228</v>
       </c>
       <c r="D6">
-        <v>81.49674930007363</v>
+        <v>81.62605190157228</v>
       </c>
       <c r="E6">
-        <v>-3.474399999999999</v>
+        <v>-2.507999999999998</v>
       </c>
       <c r="F6">
-        <v>3.8656</v>
+        <v>4.832000000000001</v>
       </c>
       <c r="G6">
         <v>15.7</v>
@@ -1767,45 +1767,45 @@
         <v>1.87</v>
       </c>
       <c r="M6">
-        <v>0.2068096</v>
+        <v>0.2623776</v>
       </c>
       <c r="N6">
-        <v>1.6631904</v>
+        <v>1.6076224</v>
       </c>
       <c r="O6">
-        <v>0.299374272</v>
+        <v>0.289372032</v>
       </c>
       <c r="P6">
-        <v>1.363816128</v>
+        <v>1.318250368</v>
       </c>
       <c r="Q6">
-        <v>5.893816128000001</v>
+        <v>5.848250368</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1066602547552433</v>
+        <v>0.1071893845836849</v>
       </c>
       <c r="T6">
-        <v>1.026191328330506</v>
+        <v>1.035113217397377</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.18</v>
       </c>
       <c r="W6">
-        <v>0.04387</v>
+        <v>0.044526</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>9.042133440613975</v>
+        <v>7.127132804019855</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1040562153545007</v>
+        <v>0.1039867461439678</v>
       </c>
       <c r="C7">
-        <v>92.49405190157228</v>
+        <v>91.62510532112748</v>
       </c>
       <c r="D7">
-        <v>81.62605190157228</v>
+        <v>81.72350532112748</v>
       </c>
       <c r="E7">
-        <v>-2.507999999999998</v>
+        <v>-1.541599999999998</v>
       </c>
       <c r="F7">
-        <v>4.832000000000001</v>
+        <v>5.798400000000001</v>
       </c>
       <c r="G7">
         <v>15.7</v>
@@ -1849,45 +1849,45 @@
         <v>1.87</v>
       </c>
       <c r="M7">
-        <v>0.2623776</v>
+        <v>0.3206515200000001</v>
       </c>
       <c r="N7">
-        <v>1.6076224</v>
+        <v>1.54934848</v>
       </c>
       <c r="O7">
-        <v>0.289372032</v>
+        <v>0.2788827263999999</v>
       </c>
       <c r="P7">
-        <v>1.318250368</v>
+        <v>1.2704657536</v>
       </c>
       <c r="Q7">
-        <v>5.848250368</v>
+        <v>5.8004657536</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1071893845836849</v>
+        <v>0.1077297724935827</v>
       </c>
       <c r="T7">
-        <v>1.035113217397377</v>
+        <v>1.044224933891203</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.18</v>
       </c>
       <c r="W7">
-        <v>0.044526</v>
+        <v>0.045346</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>7.127132804019855</v>
+        <v>5.831876299853497</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1039867461439678</v>
+        <v>0.1038762769334349</v>
       </c>
       <c r="C8">
-        <v>91.62510532112748</v>
+        <v>90.81415487112452</v>
       </c>
       <c r="D8">
-        <v>81.72350532112748</v>
+        <v>81.87895487112451</v>
       </c>
       <c r="E8">
-        <v>-1.541599999999999</v>
+        <v>-0.5751999999999997</v>
       </c>
       <c r="F8">
-        <v>5.7984</v>
+        <v>6.764799999999999</v>
       </c>
       <c r="G8">
         <v>15.7</v>
@@ -1931,28 +1931,28 @@
         <v>1.87</v>
       </c>
       <c r="M8">
-        <v>0.32065152</v>
+        <v>0.37409344</v>
       </c>
       <c r="N8">
-        <v>1.54934848</v>
+        <v>1.49590656</v>
       </c>
       <c r="O8">
-        <v>0.2788827264</v>
+        <v>0.2692631808</v>
       </c>
       <c r="P8">
-        <v>1.2704657536</v>
+        <v>1.2266433792</v>
       </c>
       <c r="Q8">
-        <v>5.8004657536</v>
+        <v>5.7566433792</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1077297724935827</v>
+        <v>0.1082817816488547</v>
       </c>
       <c r="T8">
-        <v>1.044224933891203</v>
+        <v>1.053532601277369</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.831876299853499</v>
+        <v>4.998751114160141</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1038762769334349</v>
+        <v>0.103929807722902</v>
       </c>
       <c r="C9">
-        <v>90.81415487112452</v>
+        <v>89.77235388036452</v>
       </c>
       <c r="D9">
-        <v>81.87895487112451</v>
+        <v>81.80355388036452</v>
       </c>
       <c r="E9">
-        <v>-0.5751999999999979</v>
+        <v>0.3912000000000013</v>
       </c>
       <c r="F9">
-        <v>6.764800000000001</v>
+        <v>7.7312</v>
       </c>
       <c r="G9">
         <v>15.7</v>
@@ -2013,45 +2013,45 @@
         <v>1.87</v>
       </c>
       <c r="M9">
-        <v>0.3740934400000001</v>
+        <v>0.44686336</v>
       </c>
       <c r="N9">
-        <v>1.49590656</v>
+        <v>1.42313664</v>
       </c>
       <c r="O9">
-        <v>0.2692631808</v>
+        <v>0.2561645952</v>
       </c>
       <c r="P9">
-        <v>1.2266433792</v>
+        <v>1.1669720448</v>
       </c>
       <c r="Q9">
-        <v>5.7566433792</v>
+        <v>5.696972044800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1082817816488547</v>
+        <v>0.1088457910031543</v>
       </c>
       <c r="T9">
-        <v>1.053532601277369</v>
+        <v>1.063042609258887</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V9">
         <v>0.18</v>
       </c>
       <c r="W9">
-        <v>0.045346</v>
+        <v>0.04739600000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.998751114160141</v>
+        <v>4.184724386443319</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.103929807722902</v>
+        <v>0.1040981385123691</v>
       </c>
       <c r="C10">
-        <v>89.77235388036452</v>
+        <v>88.56975325445647</v>
       </c>
       <c r="D10">
-        <v>81.80355388036452</v>
+        <v>81.56735325445646</v>
       </c>
       <c r="E10">
-        <v>0.3912000000000013</v>
+        <v>1.357600000000001</v>
       </c>
       <c r="F10">
-        <v>7.7312</v>
+        <v>8.6976</v>
       </c>
       <c r="G10">
         <v>15.7</v>
@@ -2095,45 +2095,45 @@
         <v>1.87</v>
       </c>
       <c r="M10">
-        <v>0.44686336</v>
+        <v>0.53316288</v>
       </c>
       <c r="N10">
-        <v>1.42313664</v>
+        <v>1.33683712</v>
       </c>
       <c r="O10">
-        <v>0.2561645952</v>
+        <v>0.2406306816</v>
       </c>
       <c r="P10">
-        <v>1.1669720448</v>
+        <v>1.0962064384</v>
       </c>
       <c r="Q10">
-        <v>5.696972044800001</v>
+        <v>5.626206438400001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1088457910031543</v>
+        <v>0.1094221961674386</v>
       </c>
       <c r="T10">
-        <v>1.063042609258887</v>
+        <v>1.072761628404833</v>
       </c>
       <c r="U10">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V10">
         <v>0.18</v>
       </c>
       <c r="W10">
-        <v>0.04739600000000001</v>
+        <v>0.05026600000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.184724386443319</v>
+        <v>3.507370955757461</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1040981385123691</v>
+        <v>0.1042664693018362</v>
       </c>
       <c r="C11">
-        <v>88.56975325445647</v>
+        <v>87.36851271881234</v>
       </c>
       <c r="D11">
-        <v>81.56735325445646</v>
+        <v>81.33251271881234</v>
       </c>
       <c r="E11">
-        <v>1.357600000000001</v>
+        <v>2.324000000000001</v>
       </c>
       <c r="F11">
-        <v>8.6976</v>
+        <v>9.664</v>
       </c>
       <c r="G11">
         <v>15.7</v>
@@ -2177,45 +2177,45 @@
         <v>1.87</v>
       </c>
       <c r="M11">
-        <v>0.53316288</v>
+        <v>0.6194624</v>
       </c>
       <c r="N11">
-        <v>1.33683712</v>
+        <v>1.2505376</v>
       </c>
       <c r="O11">
-        <v>0.2406306816</v>
+        <v>0.225096768</v>
       </c>
       <c r="P11">
-        <v>1.0962064384</v>
+        <v>1.025440832</v>
       </c>
       <c r="Q11">
-        <v>5.626206438400001</v>
+        <v>5.555440832</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1094221961674386</v>
+        <v>0.1100114103353735</v>
       </c>
       <c r="T11">
-        <v>1.072761628404833</v>
+        <v>1.082696625754023</v>
       </c>
       <c r="U11">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.18</v>
       </c>
       <c r="W11">
-        <v>0.05026600000000001</v>
+        <v>0.052562</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.507370955757461</v>
+        <v>3.018746577677677</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1042664693018362</v>
+        <v>0.1052835000913033</v>
       </c>
       <c r="C12">
-        <v>87.36851271881234</v>
+        <v>85.01151415798813</v>
       </c>
       <c r="D12">
-        <v>81.33251271881234</v>
+        <v>79.94191415798812</v>
       </c>
       <c r="E12">
-        <v>2.324000000000003</v>
+        <v>3.290400000000001</v>
       </c>
       <c r="F12">
-        <v>9.664000000000001</v>
+        <v>10.6304</v>
       </c>
       <c r="G12">
         <v>15.7</v>
@@ -2259,45 +2259,45 @@
         <v>1.87</v>
       </c>
       <c r="M12">
-        <v>0.6194624000000002</v>
+        <v>0.8057843200000001</v>
       </c>
       <c r="N12">
-        <v>1.2505376</v>
+        <v>1.06421568</v>
       </c>
       <c r="O12">
-        <v>0.225096768</v>
+        <v>0.1915588224</v>
       </c>
       <c r="P12">
-        <v>1.025440832</v>
+        <v>0.8726568576</v>
       </c>
       <c r="Q12">
-        <v>5.555440832</v>
+        <v>5.4026568576</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1100114103353735</v>
+        <v>0.1106138652711273</v>
       </c>
       <c r="T12">
-        <v>1.082696625754023</v>
+        <v>1.09285488147061</v>
       </c>
       <c r="U12">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.18</v>
       </c>
       <c r="W12">
-        <v>0.052562</v>
+        <v>0.06215600000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>3.018746577677676</v>
+        <v>2.320720264201716</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1052835000913033</v>
+        <v>0.1053411308807704</v>
       </c>
       <c r="C13">
-        <v>85.01151415798813</v>
+        <v>83.96773713211898</v>
       </c>
       <c r="D13">
-        <v>79.94191415798812</v>
+        <v>79.86453713211898</v>
       </c>
       <c r="E13">
-        <v>3.290400000000001</v>
+        <v>4.256800000000001</v>
       </c>
       <c r="F13">
-        <v>10.6304</v>
+        <v>11.5968</v>
       </c>
       <c r="G13">
         <v>15.7</v>
@@ -2341,28 +2341,28 @@
         <v>1.87</v>
       </c>
       <c r="M13">
-        <v>0.8057843200000001</v>
+        <v>0.8790374400000001</v>
       </c>
       <c r="N13">
-        <v>1.06421568</v>
+        <v>0.99096256</v>
       </c>
       <c r="O13">
-        <v>0.1915588224</v>
+        <v>0.1783732608</v>
       </c>
       <c r="P13">
-        <v>0.8726568576</v>
+        <v>0.8125892992000001</v>
       </c>
       <c r="Q13">
-        <v>5.4026568576</v>
+        <v>5.3425892992</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1106138652711273</v>
+        <v>0.1112300123645118</v>
       </c>
       <c r="T13">
-        <v>1.09285488147061</v>
+        <v>1.103244006635302</v>
       </c>
       <c r="U13">
         <v>0.07580000000000001</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.320720264201716</v>
+        <v>2.127326908851573</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1053411308807704</v>
+        <v>0.1069124816702375</v>
       </c>
       <c r="C14">
-        <v>83.96773713211898</v>
+        <v>80.94782531189621</v>
       </c>
       <c r="D14">
-        <v>79.86453713211898</v>
+        <v>77.8110253118962</v>
       </c>
       <c r="E14">
-        <v>4.256800000000001</v>
+        <v>5.223200000000001</v>
       </c>
       <c r="F14">
-        <v>11.5968</v>
+        <v>12.5632</v>
       </c>
       <c r="G14">
         <v>15.7</v>
@@ -2423,45 +2423,45 @@
         <v>1.87</v>
       </c>
       <c r="M14">
-        <v>0.8790374400000001</v>
+        <v>1.130688</v>
       </c>
       <c r="N14">
-        <v>0.99096256</v>
+        <v>0.7393120000000002</v>
       </c>
       <c r="O14">
-        <v>0.1783732608</v>
+        <v>0.13307616</v>
       </c>
       <c r="P14">
-        <v>0.8125892992000001</v>
+        <v>0.6062358400000002</v>
       </c>
       <c r="Q14">
-        <v>5.3425892992</v>
+        <v>5.13623584</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1112300123645118</v>
+        <v>0.1118603237588937</v>
       </c>
       <c r="T14">
-        <v>1.103244006635302</v>
+        <v>1.11387196226355</v>
       </c>
       <c r="U14">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V14">
         <v>0.18</v>
       </c>
       <c r="W14">
-        <v>0.06215600000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.127326908851573</v>
+        <v>1.653860304522556</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1069124816702375</v>
+        <v>0.1070865524597046</v>
       </c>
       <c r="C15">
-        <v>80.94782531189621</v>
+        <v>79.76042044114271</v>
       </c>
       <c r="D15">
-        <v>77.8110253118962</v>
+        <v>77.59002044114271</v>
       </c>
       <c r="E15">
-        <v>5.223200000000001</v>
+        <v>6.189600000000003</v>
       </c>
       <c r="F15">
-        <v>12.5632</v>
+        <v>13.5296</v>
       </c>
       <c r="G15">
         <v>15.7</v>
@@ -2505,28 +2505,28 @@
         <v>1.87</v>
       </c>
       <c r="M15">
-        <v>1.130688</v>
+        <v>1.217664</v>
       </c>
       <c r="N15">
-        <v>0.7393120000000002</v>
+        <v>0.652336</v>
       </c>
       <c r="O15">
-        <v>0.13307616</v>
+        <v>0.11742048</v>
       </c>
       <c r="P15">
-        <v>0.6062358400000002</v>
+        <v>0.53491552</v>
       </c>
       <c r="Q15">
-        <v>5.13623584</v>
+        <v>5.06491552</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1118603237588937</v>
+        <v>0.112505293557796</v>
       </c>
       <c r="T15">
-        <v>1.11387196226355</v>
+        <v>1.124747079650594</v>
       </c>
       <c r="U15">
         <v>0.09</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>1.653860304522556</v>
+        <v>1.535727425628088</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1070865524597046</v>
+        <v>0.114920245664587</v>
       </c>
       <c r="C16">
-        <v>79.76042044114271</v>
+        <v>70.00041141888951</v>
       </c>
       <c r="D16">
-        <v>77.59002044114271</v>
+        <v>68.79641141888952</v>
       </c>
       <c r="E16">
-        <v>6.189600000000003</v>
+        <v>7.156000000000003</v>
       </c>
       <c r="F16">
-        <v>13.5296</v>
+        <v>14.496</v>
       </c>
       <c r="G16">
         <v>15.7</v>
@@ -2587,45 +2587,45 @@
         <v>1.87</v>
       </c>
       <c r="M16">
-        <v>1.217664</v>
+        <v>2.1280128</v>
       </c>
       <c r="N16">
-        <v>0.652336</v>
+        <v>-0.2580128000000004</v>
       </c>
       <c r="O16">
-        <v>0.11742048</v>
+        <v>-0.04644230400000007</v>
       </c>
       <c r="P16">
-        <v>0.53491552</v>
+        <v>-0.2115704960000003</v>
       </c>
       <c r="Q16">
-        <v>5.06491552</v>
+        <v>4.318429504</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.112505293557796</v>
+        <v>0.1133920887834253</v>
       </c>
       <c r="T16">
-        <v>1.124747079650594</v>
+        <v>1.139699721143887</v>
       </c>
       <c r="U16">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.18</v>
+        <v>0.1581757402962989</v>
       </c>
       <c r="W16">
-        <v>0.0738</v>
+        <v>0.1235798013245033</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y16">
-        <v>1.535727425628088</v>
+        <v>0.8787541127572164</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.114920245664587</v>
+        <v>0.115930245664587</v>
       </c>
       <c r="C17">
-        <v>70.00041141888954</v>
+        <v>68.04322099922663</v>
       </c>
       <c r="D17">
-        <v>68.79641141888953</v>
+        <v>67.80562099922663</v>
       </c>
       <c r="E17">
-        <v>7.156</v>
+        <v>8.122400000000003</v>
       </c>
       <c r="F17">
-        <v>14.496</v>
+        <v>15.4624</v>
       </c>
       <c r="G17">
         <v>15.7</v>
@@ -2669,37 +2669,37 @@
         <v>1.87</v>
       </c>
       <c r="M17">
-        <v>2.1280128</v>
+        <v>2.26988032</v>
       </c>
       <c r="N17">
-        <v>-0.2580127999999999</v>
+        <v>-0.3998803200000003</v>
       </c>
       <c r="O17">
-        <v>-0.04644230399999998</v>
+        <v>-0.07197845760000005</v>
       </c>
       <c r="P17">
-        <v>-0.2115704959999999</v>
+        <v>-0.3279018624000002</v>
       </c>
       <c r="Q17">
-        <v>4.318429504</v>
+        <v>4.2020981376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1133920887834253</v>
+        <v>0.1141967565070375</v>
       </c>
       <c r="T17">
-        <v>1.139699721143887</v>
+        <v>1.153267574967029</v>
       </c>
       <c r="U17">
         <v>0.1468</v>
       </c>
       <c r="V17">
-        <v>0.158175740296299</v>
+        <v>0.1482897565277803</v>
       </c>
       <c r="W17">
-        <v>0.1235798013245033</v>
+        <v>0.1250310637417218</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.8787541127572165</v>
+        <v>0.8238319807098904</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.115930245664587</v>
+        <v>0.1264957408878325</v>
       </c>
       <c r="C18">
-        <v>68.04322099922663</v>
+        <v>58.1990294715136</v>
       </c>
       <c r="D18">
-        <v>67.80562099922663</v>
+        <v>58.92782947151361</v>
       </c>
       <c r="E18">
-        <v>8.122400000000003</v>
+        <v>9.088800000000003</v>
       </c>
       <c r="F18">
-        <v>15.4624</v>
+        <v>16.4288</v>
       </c>
       <c r="G18">
         <v>15.7</v>
@@ -2751,45 +2751,45 @@
         <v>1.87</v>
       </c>
       <c r="M18">
-        <v>2.26988032</v>
+        <v>3.298903040000001</v>
       </c>
       <c r="N18">
-        <v>-0.3998803200000003</v>
+        <v>-1.428903040000001</v>
       </c>
       <c r="O18">
-        <v>-0.07197845760000005</v>
+        <v>-0.2572025472000001</v>
       </c>
       <c r="P18">
-        <v>-0.3279018624000002</v>
+        <v>-1.171700492800001</v>
       </c>
       <c r="Q18">
-        <v>4.2020981376</v>
+        <v>3.3582995072</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1141967565070375</v>
+        <v>0.1154732176977795</v>
       </c>
       <c r="T18">
-        <v>1.153267574967029</v>
+        <v>1.174790544434669</v>
       </c>
       <c r="U18">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1482897565277803</v>
+        <v>0.1020339173108889</v>
       </c>
       <c r="W18">
-        <v>0.1250310637417218</v>
+        <v>0.1803115894039735</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y18">
-        <v>0.8238319807098904</v>
+        <v>0.5668550961716048</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1264957408878325</v>
+        <v>0.1280457408878325</v>
       </c>
       <c r="C19">
-        <v>58.1990294715136</v>
+        <v>56.12207791352577</v>
       </c>
       <c r="D19">
-        <v>58.92782947151361</v>
+        <v>57.81727791352578</v>
       </c>
       <c r="E19">
-        <v>9.088800000000003</v>
+        <v>10.0552</v>
       </c>
       <c r="F19">
-        <v>16.4288</v>
+        <v>17.3952</v>
       </c>
       <c r="G19">
         <v>15.7</v>
@@ -2833,37 +2833,37 @@
         <v>1.87</v>
       </c>
       <c r="M19">
-        <v>3.298903040000001</v>
+        <v>3.492956160000001</v>
       </c>
       <c r="N19">
-        <v>-1.428903040000001</v>
+        <v>-1.622956160000001</v>
       </c>
       <c r="O19">
-        <v>-0.2572025472000001</v>
+        <v>-0.2921321088000001</v>
       </c>
       <c r="P19">
-        <v>-1.171700492800001</v>
+        <v>-1.3308240512</v>
       </c>
       <c r="Q19">
-        <v>3.3582995072</v>
+        <v>3.1991759488</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1154732176977795</v>
+        <v>0.1163228910843378</v>
       </c>
       <c r="T19">
-        <v>1.174790544434669</v>
+        <v>1.189117258391189</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.1020339173108889</v>
+        <v>0.09636536634917282</v>
       </c>
       <c r="W19">
-        <v>0.1803115894039735</v>
+        <v>0.1814498344370861</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.5668550961716048</v>
+        <v>0.5353631463842935</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1280457408878325</v>
+        <v>0.1295957408878325</v>
       </c>
       <c r="C20">
-        <v>56.12207791352577</v>
+        <v>54.08621089985111</v>
       </c>
       <c r="D20">
-        <v>57.81727791352578</v>
+        <v>56.74781089985111</v>
       </c>
       <c r="E20">
-        <v>10.0552</v>
+        <v>11.0216</v>
       </c>
       <c r="F20">
-        <v>17.3952</v>
+        <v>18.3616</v>
       </c>
       <c r="G20">
         <v>15.7</v>
@@ -2915,37 +2915,37 @@
         <v>1.87</v>
       </c>
       <c r="M20">
-        <v>3.49295616</v>
+        <v>3.68700928</v>
       </c>
       <c r="N20">
-        <v>-1.62295616</v>
+        <v>-1.81700928</v>
       </c>
       <c r="O20">
-        <v>-0.2921321088</v>
+        <v>-0.3270616703999999</v>
       </c>
       <c r="P20">
-        <v>-1.3308240512</v>
+        <v>-1.4899476096</v>
       </c>
       <c r="Q20">
-        <v>3.199175948800001</v>
+        <v>3.040052390400001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1163228910843378</v>
+        <v>0.1171935440606877</v>
       </c>
       <c r="T20">
-        <v>1.189117258391189</v>
+        <v>1.203797718371327</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.09636536634917285</v>
+        <v>0.09129350496237429</v>
       </c>
       <c r="W20">
-        <v>0.1814498344370861</v>
+        <v>0.1824682642035552</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.5353631463842936</v>
+        <v>0.5071861386798571</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1295957408878325</v>
+        <v>0.1382972577458914</v>
       </c>
       <c r="C21">
-        <v>54.08621089985111</v>
+        <v>47.78136038535546</v>
       </c>
       <c r="D21">
-        <v>56.74781089985111</v>
+        <v>51.40936038535546</v>
       </c>
       <c r="E21">
-        <v>11.0216</v>
+        <v>11.988</v>
       </c>
       <c r="F21">
-        <v>18.3616</v>
+        <v>19.328</v>
       </c>
       <c r="G21">
         <v>15.7</v>
@@ -2997,45 +2997,45 @@
         <v>1.87</v>
       </c>
       <c r="M21">
-        <v>3.68700928</v>
+        <v>4.557542400000001</v>
       </c>
       <c r="N21">
-        <v>-1.81700928</v>
+        <v>-2.687542400000001</v>
       </c>
       <c r="O21">
-        <v>-0.3270616703999999</v>
+        <v>-0.4837576320000001</v>
       </c>
       <c r="P21">
-        <v>-1.4899476096</v>
+        <v>-2.203784768000001</v>
       </c>
       <c r="Q21">
-        <v>3.040052390400001</v>
+        <v>2.326215232</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1171935440606877</v>
+        <v>0.1182753594340199</v>
       </c>
       <c r="T21">
-        <v>1.203797718371327</v>
+        <v>1.22203867972505</v>
       </c>
       <c r="U21">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.09129350496237429</v>
+        <v>0.07385559375157978</v>
       </c>
       <c r="W21">
-        <v>0.1824682642035552</v>
+        <v>0.2183848509933775</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y21">
-        <v>0.5071861386798571</v>
+        <v>0.4103088541754433</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1382972577458914</v>
+        <v>0.1401972577458914</v>
       </c>
       <c r="C22">
-        <v>47.78136038535546</v>
+        <v>45.78020803063013</v>
       </c>
       <c r="D22">
-        <v>51.40936038535546</v>
+        <v>50.37460803063013</v>
       </c>
       <c r="E22">
-        <v>11.988</v>
+        <v>12.9544</v>
       </c>
       <c r="F22">
-        <v>19.328</v>
+        <v>20.2944</v>
       </c>
       <c r="G22">
         <v>15.7</v>
@@ -3079,37 +3079,37 @@
         <v>1.87</v>
       </c>
       <c r="M22">
-        <v>4.557542400000001</v>
+        <v>4.785419520000001</v>
       </c>
       <c r="N22">
-        <v>-2.687542400000001</v>
+        <v>-2.915419520000001</v>
       </c>
       <c r="O22">
-        <v>-0.4837576320000001</v>
+        <v>-0.5247755136000002</v>
       </c>
       <c r="P22">
-        <v>-2.203784768000001</v>
+        <v>-2.390644006400001</v>
       </c>
       <c r="Q22">
-        <v>2.326215232</v>
+        <v>2.139355993599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1182753594340199</v>
+        <v>0.1191927690471087</v>
       </c>
       <c r="T22">
-        <v>1.22203867972505</v>
+        <v>1.237507523772203</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.07385559375157978</v>
+        <v>0.07033866071579026</v>
       </c>
       <c r="W22">
-        <v>0.2183848509933775</v>
+        <v>0.2192141438032167</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.4103088541754433</v>
+        <v>0.3907703373099459</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1401972577458914</v>
+        <v>0.1420972577458914</v>
       </c>
       <c r="C23">
-        <v>45.78020803063013</v>
+        <v>43.81988818806555</v>
       </c>
       <c r="D23">
-        <v>50.37460803063014</v>
+        <v>49.38068818806556</v>
       </c>
       <c r="E23">
-        <v>12.9544</v>
+        <v>13.9208</v>
       </c>
       <c r="F23">
-        <v>20.2944</v>
+        <v>21.2608</v>
       </c>
       <c r="G23">
         <v>15.7</v>
@@ -3161,37 +3161,37 @@
         <v>1.87</v>
       </c>
       <c r="M23">
-        <v>4.78541952</v>
+        <v>5.01329664</v>
       </c>
       <c r="N23">
-        <v>-2.91541952</v>
+        <v>-3.14329664</v>
       </c>
       <c r="O23">
-        <v>-0.5247755136000001</v>
+        <v>-0.5657933951999999</v>
       </c>
       <c r="P23">
-        <v>-2.390644006400001</v>
+        <v>-2.5775032448</v>
       </c>
       <c r="Q23">
-        <v>2.1393559936</v>
+        <v>1.9524967552</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1191927690471087</v>
+        <v>0.1201337019836101</v>
       </c>
       <c r="T23">
-        <v>1.237507523772203</v>
+        <v>1.253373004846205</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.07033866071579027</v>
+        <v>0.06714144886507255</v>
       </c>
       <c r="W23">
-        <v>0.2192141438032167</v>
+        <v>0.2199680463576159</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.390770337309946</v>
+        <v>0.373008049250403</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1420972577458914</v>
+        <v>0.1439972577458914</v>
       </c>
       <c r="C24">
-        <v>43.81988818806555</v>
+        <v>41.89803067620596</v>
       </c>
       <c r="D24">
-        <v>49.38068818806556</v>
+        <v>48.42523067620596</v>
       </c>
       <c r="E24">
-        <v>13.9208</v>
+        <v>14.8872</v>
       </c>
       <c r="F24">
-        <v>21.2608</v>
+        <v>22.2272</v>
       </c>
       <c r="G24">
         <v>15.7</v>
@@ -3243,37 +3243,37 @@
         <v>1.87</v>
       </c>
       <c r="M24">
-        <v>5.01329664</v>
+        <v>5.241173760000001</v>
       </c>
       <c r="N24">
-        <v>-3.14329664</v>
+        <v>-3.37117376</v>
       </c>
       <c r="O24">
-        <v>-0.5657933951999999</v>
+        <v>-0.6068112768</v>
       </c>
       <c r="P24">
-        <v>-2.5775032448</v>
+        <v>-2.7643624832</v>
       </c>
       <c r="Q24">
-        <v>1.9524967552</v>
+        <v>1.7656375168</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1201337019836101</v>
+        <v>0.121099074736644</v>
       </c>
       <c r="T24">
-        <v>1.253373004846205</v>
+        <v>1.269650576337714</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.06714144886507255</v>
+        <v>0.06422225543615634</v>
       </c>
       <c r="W24">
-        <v>0.2199680463576159</v>
+        <v>0.2206563921681543</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.373008049250403</v>
+        <v>0.3567903079786463</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1439972577458914</v>
+        <v>0.1458972577458914</v>
       </c>
       <c r="C25">
-        <v>41.89803067620596</v>
+        <v>40.01244527236237</v>
       </c>
       <c r="D25">
-        <v>48.42523067620596</v>
+        <v>47.50604527236238</v>
       </c>
       <c r="E25">
-        <v>14.8872</v>
+        <v>15.8536</v>
       </c>
       <c r="F25">
-        <v>22.2272</v>
+        <v>23.1936</v>
       </c>
       <c r="G25">
         <v>15.7</v>
@@ -3325,37 +3325,37 @@
         <v>1.87</v>
       </c>
       <c r="M25">
-        <v>5.241173760000001</v>
+        <v>5.469050880000001</v>
       </c>
       <c r="N25">
-        <v>-3.37117376</v>
+        <v>-3.599050880000001</v>
       </c>
       <c r="O25">
-        <v>-0.6068112768</v>
+        <v>-0.6478291584000001</v>
       </c>
       <c r="P25">
-        <v>-2.7643624832</v>
+        <v>-2.951221721600001</v>
       </c>
       <c r="Q25">
-        <v>1.7656375168</v>
+        <v>1.578778278399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.121099074736644</v>
+        <v>0.1220898520358104</v>
       </c>
       <c r="T25">
-        <v>1.269650576337714</v>
+        <v>1.286356504973737</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.06422225543615634</v>
+        <v>0.06154632812631649</v>
       </c>
       <c r="W25">
-        <v>0.2206563921681543</v>
+        <v>0.2212873758278146</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3567903079786463</v>
+        <v>0.3419240451462027</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1458972577458914</v>
+        <v>0.1477972577458914</v>
       </c>
       <c r="C26">
-        <v>40.01244527236237</v>
+        <v>38.16110495129651</v>
       </c>
       <c r="D26">
-        <v>47.50604527236238</v>
+        <v>46.62110495129651</v>
       </c>
       <c r="E26">
-        <v>15.8536</v>
+        <v>16.82</v>
       </c>
       <c r="F26">
-        <v>23.1936</v>
+        <v>24.16</v>
       </c>
       <c r="G26">
         <v>15.7</v>
@@ -3407,37 +3407,37 @@
         <v>1.87</v>
       </c>
       <c r="M26">
-        <v>5.46905088</v>
+        <v>5.696928000000001</v>
       </c>
       <c r="N26">
-        <v>-3.59905088</v>
+        <v>-3.826928000000001</v>
       </c>
       <c r="O26">
-        <v>-0.6478291584</v>
+        <v>-0.6888470400000001</v>
       </c>
       <c r="P26">
-        <v>-2.9512217216</v>
+        <v>-3.13808096</v>
       </c>
       <c r="Q26">
-        <v>1.5787782784</v>
+        <v>1.39191904</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1220898520358104</v>
+        <v>0.1231070500629545</v>
       </c>
       <c r="T26">
-        <v>1.286356504973737</v>
+        <v>1.303507925040053</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.0615463281263165</v>
+        <v>0.05908447500126383</v>
       </c>
       <c r="W26">
-        <v>0.2212873758278146</v>
+        <v>0.221867880794702</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3419240451462028</v>
+        <v>0.3282470833403547</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1477972577458914</v>
+        <v>0.1496972577458914</v>
       </c>
       <c r="C27">
-        <v>38.16110495129651</v>
+        <v>36.34213096301944</v>
       </c>
       <c r="D27">
-        <v>46.62110495129651</v>
+        <v>45.76853096301945</v>
       </c>
       <c r="E27">
-        <v>16.82</v>
+        <v>17.7864</v>
       </c>
       <c r="F27">
-        <v>24.16</v>
+        <v>25.1264</v>
       </c>
       <c r="G27">
         <v>15.7</v>
@@ -3489,37 +3489,37 @@
         <v>1.87</v>
       </c>
       <c r="M27">
-        <v>5.696928000000001</v>
+        <v>5.92480512</v>
       </c>
       <c r="N27">
-        <v>-3.826928000000001</v>
+        <v>-4.05480512</v>
       </c>
       <c r="O27">
-        <v>-0.6888470400000001</v>
+        <v>-0.7298649216</v>
       </c>
       <c r="P27">
-        <v>-3.13808096</v>
+        <v>-3.3249401984</v>
       </c>
       <c r="Q27">
-        <v>1.39191904</v>
+        <v>1.2050598016</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1231070500629545</v>
+        <v>0.1241517399286702</v>
       </c>
       <c r="T27">
-        <v>1.303507925040053</v>
+        <v>1.321122897000054</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.05908447500126383</v>
+        <v>0.05681199519352292</v>
       </c>
       <c r="W27">
-        <v>0.221867880794702</v>
+        <v>0.2224037315333673</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3282470833403547</v>
+        <v>0.3156221955195718</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1496972577458914</v>
+        <v>0.1515972577458914</v>
       </c>
       <c r="C28">
-        <v>36.34213096301944</v>
+        <v>34.55377951850657</v>
       </c>
       <c r="D28">
-        <v>45.76853096301945</v>
+        <v>44.94657951850657</v>
       </c>
       <c r="E28">
-        <v>17.7864</v>
+        <v>18.7528</v>
       </c>
       <c r="F28">
-        <v>25.1264</v>
+        <v>26.0928</v>
       </c>
       <c r="G28">
         <v>15.7</v>
@@ -3571,37 +3571,37 @@
         <v>1.87</v>
       </c>
       <c r="M28">
-        <v>5.92480512</v>
+        <v>6.152682240000001</v>
       </c>
       <c r="N28">
-        <v>-4.05480512</v>
+        <v>-4.282682240000001</v>
       </c>
       <c r="O28">
-        <v>-0.7298649216</v>
+        <v>-0.7708828032000001</v>
       </c>
       <c r="P28">
-        <v>-3.3249401984</v>
+        <v>-3.511799436800001</v>
       </c>
       <c r="Q28">
-        <v>1.2050598016</v>
+        <v>1.0182005632</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1241517399286702</v>
+        <v>0.1252250514345424</v>
       </c>
       <c r="T28">
-        <v>1.321122897000054</v>
+        <v>1.339220470931562</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.05681199519352292</v>
+        <v>0.05470784722339243</v>
       </c>
       <c r="W28">
-        <v>0.2224037315333673</v>
+        <v>0.2228998896247241</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3156221955195718</v>
+        <v>0.3039324845744025</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1515972577458914</v>
+        <v>0.1534972577458914</v>
       </c>
       <c r="C29">
-        <v>34.55377951850657</v>
+        <v>32.79442988475955</v>
       </c>
       <c r="D29">
-        <v>44.94657951850657</v>
+        <v>44.15362988475956</v>
       </c>
       <c r="E29">
-        <v>18.7528</v>
+        <v>19.7192</v>
       </c>
       <c r="F29">
-        <v>26.0928</v>
+        <v>27.0592</v>
       </c>
       <c r="G29">
         <v>15.7</v>
@@ -3653,37 +3653,37 @@
         <v>1.87</v>
       </c>
       <c r="M29">
-        <v>6.152682240000001</v>
+        <v>6.380559360000001</v>
       </c>
       <c r="N29">
-        <v>-4.282682240000001</v>
+        <v>-4.510559360000001</v>
       </c>
       <c r="O29">
-        <v>-0.7708828032000001</v>
+        <v>-0.8119006848000002</v>
       </c>
       <c r="P29">
-        <v>-3.511799436800001</v>
+        <v>-3.698658675200001</v>
       </c>
       <c r="Q29">
-        <v>1.0182005632</v>
+        <v>0.8313413247999994</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1252250514345424</v>
+        <v>0.126328177148911</v>
       </c>
       <c r="T29">
-        <v>1.339220470931562</v>
+        <v>1.357820755250056</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05470784722339243</v>
+        <v>0.0527539955368427</v>
       </c>
       <c r="W29">
-        <v>0.2228998896247241</v>
+        <v>0.2233606078524125</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3039324845744025</v>
+        <v>0.2930777529824595</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1534972577458914</v>
+        <v>0.1553972577458914</v>
       </c>
       <c r="C30">
-        <v>32.79442988475955</v>
+        <v>31.0625737181869</v>
       </c>
       <c r="D30">
-        <v>44.15362988475956</v>
+        <v>43.38817371818691</v>
       </c>
       <c r="E30">
-        <v>19.7192</v>
+        <v>20.6856</v>
       </c>
       <c r="F30">
-        <v>27.0592</v>
+        <v>28.0256</v>
       </c>
       <c r="G30">
         <v>15.7</v>
@@ -3735,37 +3735,37 @@
         <v>1.87</v>
       </c>
       <c r="M30">
-        <v>6.380559360000001</v>
+        <v>6.608436480000002</v>
       </c>
       <c r="N30">
-        <v>-4.510559360000001</v>
+        <v>-4.738436480000002</v>
       </c>
       <c r="O30">
-        <v>-0.8119006848000002</v>
+        <v>-0.8529185664000003</v>
       </c>
       <c r="P30">
-        <v>-3.698658675200001</v>
+        <v>-3.885517913600001</v>
       </c>
       <c r="Q30">
-        <v>0.8313413247999994</v>
+        <v>0.6444820863999992</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.126328177148911</v>
+        <v>0.1274623768270647</v>
       </c>
       <c r="T30">
-        <v>1.357820755250056</v>
+        <v>1.376944991239493</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.0527539955368427</v>
+        <v>0.05093489224246881</v>
       </c>
       <c r="W30">
-        <v>0.2233606078524125</v>
+        <v>0.2237895524092259</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2930777529824595</v>
+        <v>0.2829716235692712</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1553972577458914</v>
+        <v>0.1572972577458914</v>
       </c>
       <c r="C31">
-        <v>31.06257371818694</v>
+        <v>29.35680548858944</v>
       </c>
       <c r="D31">
-        <v>43.38817371818693</v>
+        <v>42.64880548858943</v>
       </c>
       <c r="E31">
-        <v>20.6856</v>
+        <v>21.652</v>
       </c>
       <c r="F31">
-        <v>28.0256</v>
+        <v>28.992</v>
       </c>
       <c r="G31">
         <v>15.7</v>
@@ -3817,37 +3817,37 @@
         <v>1.87</v>
       </c>
       <c r="M31">
-        <v>6.60843648</v>
+        <v>6.8363136</v>
       </c>
       <c r="N31">
-        <v>-4.73843648</v>
+        <v>-4.966313599999999</v>
       </c>
       <c r="O31">
-        <v>-0.8529185664</v>
+        <v>-0.8939364479999998</v>
       </c>
       <c r="P31">
-        <v>-3.8855179136</v>
+        <v>-4.072377152</v>
       </c>
       <c r="Q31">
-        <v>0.6444820864000005</v>
+        <v>0.4576228480000006</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1274623768270647</v>
+        <v>0.1286289822103084</v>
       </c>
       <c r="T31">
-        <v>1.376944991239493</v>
+        <v>1.396615633971486</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.05093489224246883</v>
+        <v>0.0492370625010532</v>
       </c>
       <c r="W31">
-        <v>0.2237895524092259</v>
+        <v>0.2241899006622517</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2829716235692713</v>
+        <v>0.2735392361169623</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1572972577458914</v>
+        <v>0.1591972577458914</v>
       </c>
       <c r="C32">
-        <v>29.35680548858944</v>
+        <v>27.67581386583693</v>
       </c>
       <c r="D32">
-        <v>42.64880548858943</v>
+        <v>41.93421386583693</v>
       </c>
       <c r="E32">
-        <v>21.652</v>
+        <v>22.6184</v>
       </c>
       <c r="F32">
-        <v>28.992</v>
+        <v>29.9584</v>
       </c>
       <c r="G32">
         <v>15.7</v>
@@ -3899,37 +3899,37 @@
         <v>1.87</v>
       </c>
       <c r="M32">
-        <v>6.8363136</v>
+        <v>7.064190720000001</v>
       </c>
       <c r="N32">
-        <v>-4.966313599999999</v>
+        <v>-5.194190720000001</v>
       </c>
       <c r="O32">
-        <v>-0.8939364479999998</v>
+        <v>-0.9349543296000001</v>
       </c>
       <c r="P32">
-        <v>-4.072377152</v>
+        <v>-4.259236390400001</v>
       </c>
       <c r="Q32">
-        <v>0.4576228480000006</v>
+        <v>0.2707636095999995</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1286289822103084</v>
+        <v>0.1298294022423419</v>
       </c>
       <c r="T32">
-        <v>1.396615633971486</v>
+        <v>1.416856440260928</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0492370625010532</v>
+        <v>0.04764877016230955</v>
       </c>
       <c r="W32">
-        <v>0.2241899006622517</v>
+        <v>0.2245644199957274</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2735392361169623</v>
+        <v>0.2647153897906086</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1591972577458914</v>
+        <v>0.1610972577458914</v>
       </c>
       <c r="C33">
-        <v>27.67581386583693</v>
+        <v>26.01837395818631</v>
       </c>
       <c r="D33">
-        <v>41.93421386583693</v>
+        <v>41.24317395818631</v>
       </c>
       <c r="E33">
-        <v>22.6184</v>
+        <v>23.5848</v>
       </c>
       <c r="F33">
-        <v>29.9584</v>
+        <v>30.9248</v>
       </c>
       <c r="G33">
         <v>15.7</v>
@@ -3981,37 +3981,37 @@
         <v>1.87</v>
       </c>
       <c r="M33">
-        <v>7.064190720000001</v>
+        <v>7.292067840000001</v>
       </c>
       <c r="N33">
-        <v>-5.194190720000001</v>
+        <v>-5.42206784</v>
       </c>
       <c r="O33">
-        <v>-0.9349543296000001</v>
+        <v>-0.9759722112</v>
       </c>
       <c r="P33">
-        <v>-4.259236390400001</v>
+        <v>-4.4460956288</v>
       </c>
       <c r="Q33">
-        <v>0.2707636095999995</v>
+        <v>0.08390437120000005</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1298294022423419</v>
+        <v>0.1310651287459057</v>
       </c>
       <c r="T33">
-        <v>1.416856440260928</v>
+        <v>1.437692564382412</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.04764877016230955</v>
+        <v>0.04615974609473737</v>
       </c>
       <c r="W33">
-        <v>0.2245644199957274</v>
+        <v>0.2249155318708609</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2647153897906086</v>
+        <v>0.2564430338596521</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1610972577458914</v>
+        <v>0.1629972577458914</v>
       </c>
       <c r="C34">
-        <v>26.01837395818631</v>
+        <v>24.38334030559301</v>
       </c>
       <c r="D34">
-        <v>41.24317395818631</v>
+        <v>40.57454030559301</v>
       </c>
       <c r="E34">
-        <v>23.5848</v>
+        <v>24.5512</v>
       </c>
       <c r="F34">
-        <v>30.9248</v>
+        <v>31.8912</v>
       </c>
       <c r="G34">
         <v>15.7</v>
@@ -4063,37 +4063,37 @@
         <v>1.87</v>
       </c>
       <c r="M34">
-        <v>7.292067840000001</v>
+        <v>7.519944960000001</v>
       </c>
       <c r="N34">
-        <v>-5.42206784</v>
+        <v>-5.649944960000001</v>
       </c>
       <c r="O34">
-        <v>-0.9759722112</v>
+        <v>-1.0169900928</v>
       </c>
       <c r="P34">
-        <v>-4.4460956288</v>
+        <v>-4.6329548672</v>
       </c>
       <c r="Q34">
-        <v>0.08390437120000005</v>
+        <v>-0.1029548672000002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1310651287459057</v>
+        <v>0.1323377426077849</v>
       </c>
       <c r="T34">
-        <v>1.437692564382412</v>
+        <v>1.459150662358269</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04615974609473737</v>
+        <v>0.04476096591004836</v>
       </c>
       <c r="W34">
-        <v>0.2249155318708609</v>
+        <v>0.2252453642384106</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2564430338596521</v>
+        <v>0.248672032833602</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1629972577458914</v>
+        <v>0.1648972577458914</v>
       </c>
       <c r="C35">
-        <v>24.38334030559301</v>
+        <v>22.76964054370335</v>
       </c>
       <c r="D35">
-        <v>40.57454030559301</v>
+        <v>39.92724054370335</v>
       </c>
       <c r="E35">
-        <v>24.5512</v>
+        <v>25.51760000000001</v>
       </c>
       <c r="F35">
-        <v>31.8912</v>
+        <v>32.85760000000001</v>
       </c>
       <c r="G35">
         <v>15.7</v>
@@ -4145,37 +4145,37 @@
         <v>1.87</v>
       </c>
       <c r="M35">
-        <v>7.519944960000001</v>
+        <v>7.747822080000001</v>
       </c>
       <c r="N35">
-        <v>-5.649944960000001</v>
+        <v>-5.877822080000001</v>
       </c>
       <c r="O35">
-        <v>-1.0169900928</v>
+        <v>-1.0580079744</v>
       </c>
       <c r="P35">
-        <v>-4.6329548672</v>
+        <v>-4.819814105600001</v>
       </c>
       <c r="Q35">
-        <v>-0.1029548672000002</v>
+        <v>-0.2898141056000005</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1323377426077849</v>
+        <v>0.1336489205260847</v>
       </c>
       <c r="T35">
-        <v>1.459150662358269</v>
+        <v>1.481259005727334</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04476096591004836</v>
+        <v>0.04344446691269399</v>
       </c>
       <c r="W35">
-        <v>0.2252453642384106</v>
+        <v>0.2255557947019868</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.248672032833602</v>
+        <v>0.2413581495149666</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1648972577458914</v>
+        <v>0.1667972577458914</v>
       </c>
       <c r="C36">
-        <v>22.76964054370335</v>
+        <v>21.1762696648066</v>
       </c>
       <c r="D36">
-        <v>39.92724054370335</v>
+        <v>39.30026966480661</v>
       </c>
       <c r="E36">
-        <v>25.51760000000001</v>
+        <v>26.48400000000001</v>
       </c>
       <c r="F36">
-        <v>32.85760000000001</v>
+        <v>33.82400000000001</v>
       </c>
       <c r="G36">
         <v>15.7</v>
@@ -4227,37 +4227,37 @@
         <v>1.87</v>
       </c>
       <c r="M36">
-        <v>7.747822080000001</v>
+        <v>7.975699200000002</v>
       </c>
       <c r="N36">
-        <v>-5.877822080000001</v>
+        <v>-6.105699200000002</v>
       </c>
       <c r="O36">
-        <v>-1.0580079744</v>
+        <v>-1.099025856</v>
       </c>
       <c r="P36">
-        <v>-4.819814105600001</v>
+        <v>-5.006673344000001</v>
       </c>
       <c r="Q36">
-        <v>-0.2898141056000005</v>
+        <v>-0.4766733440000008</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1336489205260847</v>
+        <v>0.1350004423803322</v>
       </c>
       <c r="T36">
-        <v>1.481259005727334</v>
+        <v>1.504047605815447</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04344446691269399</v>
+        <v>0.04220319642947416</v>
       </c>
       <c r="W36">
-        <v>0.2255557947019868</v>
+        <v>0.22584848628193</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2413581495149666</v>
+        <v>0.2344622023859676</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1667972577458914</v>
+        <v>0.1686972577458914</v>
       </c>
       <c r="C37">
-        <v>21.1762696648066</v>
+        <v>19.60228481114352</v>
       </c>
       <c r="D37">
-        <v>39.30026966480661</v>
+        <v>38.69268481114353</v>
       </c>
       <c r="E37">
-        <v>26.48400000000001</v>
+        <v>27.45040000000001</v>
       </c>
       <c r="F37">
-        <v>33.82400000000001</v>
+        <v>34.79040000000001</v>
       </c>
       <c r="G37">
         <v>15.7</v>
@@ -4309,37 +4309,37 @@
         <v>1.87</v>
       </c>
       <c r="M37">
-        <v>7.975699200000002</v>
+        <v>8.203576320000002</v>
       </c>
       <c r="N37">
-        <v>-6.105699200000002</v>
+        <v>-6.333576320000001</v>
       </c>
       <c r="O37">
-        <v>-1.099025856</v>
+        <v>-1.1400437376</v>
       </c>
       <c r="P37">
-        <v>-5.006673344000001</v>
+        <v>-5.193532582400001</v>
       </c>
       <c r="Q37">
-        <v>-0.4766733440000008</v>
+        <v>-0.6635325824000011</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1350004423803322</v>
+        <v>0.1363941992925249</v>
       </c>
       <c r="T37">
-        <v>1.504047605815447</v>
+        <v>1.527548349656313</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04220319642947416</v>
+        <v>0.04103088541754433</v>
       </c>
       <c r="W37">
-        <v>0.22584848628193</v>
+        <v>0.2261249172185431</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2344622023859676</v>
+        <v>0.2279493634308019</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1686972577458914</v>
+        <v>0.1705972577458914</v>
       </c>
       <c r="C38">
-        <v>19.60228481114353</v>
+        <v>18.04680054383644</v>
       </c>
       <c r="D38">
-        <v>38.69268481114353</v>
+        <v>38.10360054383644</v>
       </c>
       <c r="E38">
-        <v>27.4504</v>
+        <v>28.4168</v>
       </c>
       <c r="F38">
-        <v>34.7904</v>
+        <v>35.7568</v>
       </c>
       <c r="G38">
         <v>15.7</v>
@@ -4391,37 +4391,37 @@
         <v>1.87</v>
       </c>
       <c r="M38">
-        <v>8.20357632</v>
+        <v>8.43145344</v>
       </c>
       <c r="N38">
-        <v>-6.33357632</v>
+        <v>-6.56145344</v>
       </c>
       <c r="O38">
-        <v>-1.1400437376</v>
+        <v>-1.1810616192</v>
       </c>
       <c r="P38">
-        <v>-5.1935325824</v>
+        <v>-5.3803918208</v>
       </c>
       <c r="Q38">
-        <v>-0.6635325823999993</v>
+        <v>-0.8503918207999996</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1363941992925249</v>
+        <v>0.1378322024558983</v>
       </c>
       <c r="T38">
-        <v>1.527548349656313</v>
+        <v>1.551795148857206</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04103088541754434</v>
+        <v>0.03992194256842151</v>
       </c>
       <c r="W38">
-        <v>0.2261249172185431</v>
+        <v>0.2263864059423662</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2279493634308019</v>
+        <v>0.221788569824564</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1705972577458914</v>
+        <v>0.1724972577458914</v>
       </c>
       <c r="C39">
-        <v>18.04680054383644</v>
+        <v>16.50898453751298</v>
       </c>
       <c r="D39">
-        <v>38.10360054383644</v>
+        <v>37.53218453751298</v>
       </c>
       <c r="E39">
-        <v>28.4168</v>
+        <v>29.3832</v>
       </c>
       <c r="F39">
-        <v>35.7568</v>
+        <v>36.7232</v>
       </c>
       <c r="G39">
         <v>15.7</v>
@@ -4473,37 +4473,37 @@
         <v>1.87</v>
       </c>
       <c r="M39">
-        <v>8.43145344</v>
+        <v>8.659330560000001</v>
       </c>
       <c r="N39">
-        <v>-6.56145344</v>
+        <v>-6.789330560000001</v>
       </c>
       <c r="O39">
-        <v>-1.1810616192</v>
+        <v>-1.2220795008</v>
       </c>
       <c r="P39">
-        <v>-5.3803918208</v>
+        <v>-5.5672510592</v>
       </c>
       <c r="Q39">
-        <v>-0.8503918207999996</v>
+        <v>-1.0372510592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1378322024558983</v>
+        <v>0.1393165928180902</v>
       </c>
       <c r="T39">
-        <v>1.551795148857206</v>
+        <v>1.576824102871032</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03992194256842151</v>
+        <v>0.03887136513241041</v>
       </c>
       <c r="W39">
-        <v>0.2263864059423662</v>
+        <v>0.2266341321017776</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.221788569824564</v>
+        <v>0.2159520285133912</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1724972577458914</v>
+        <v>0.1743972577458914</v>
       </c>
       <c r="C40">
-        <v>16.50898453751298</v>
+        <v>14.98805365659651</v>
       </c>
       <c r="D40">
-        <v>37.53218453751298</v>
+        <v>36.9776536565965</v>
       </c>
       <c r="E40">
-        <v>29.3832</v>
+        <v>30.3496</v>
       </c>
       <c r="F40">
-        <v>36.7232</v>
+        <v>37.6896</v>
       </c>
       <c r="G40">
         <v>15.7</v>
@@ -4555,37 +4555,37 @@
         <v>1.87</v>
       </c>
       <c r="M40">
-        <v>8.659330560000001</v>
+        <v>8.887207679999999</v>
       </c>
       <c r="N40">
-        <v>-6.789330560000001</v>
+        <v>-7.017207679999999</v>
       </c>
       <c r="O40">
-        <v>-1.2220795008</v>
+        <v>-1.2630973824</v>
       </c>
       <c r="P40">
-        <v>-5.5672510592</v>
+        <v>-5.7541102976</v>
       </c>
       <c r="Q40">
-        <v>-1.0372510592</v>
+        <v>-1.224110297599999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1393165928180902</v>
+        <v>0.1408496517167474</v>
       </c>
       <c r="T40">
-        <v>1.576824102871032</v>
+        <v>1.602673678327935</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03887136513241041</v>
+        <v>0.03787466346234862</v>
       </c>
       <c r="W40">
-        <v>0.2266341321017776</v>
+        <v>0.2268691543555782</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2159520285133912</v>
+        <v>0.2104147970130479</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1743972577458914</v>
+        <v>0.1762972577458914</v>
       </c>
       <c r="C41">
-        <v>14.98805365659651</v>
+        <v>13.4832703743643</v>
       </c>
       <c r="D41">
-        <v>36.9776536565965</v>
+        <v>36.43927037436431</v>
       </c>
       <c r="E41">
-        <v>30.3496</v>
+        <v>31.31600000000001</v>
       </c>
       <c r="F41">
-        <v>37.6896</v>
+        <v>38.65600000000001</v>
       </c>
       <c r="G41">
         <v>15.7</v>
@@ -4637,37 +4637,37 @@
         <v>1.87</v>
       </c>
       <c r="M41">
-        <v>8.887207679999999</v>
+        <v>9.115084800000002</v>
       </c>
       <c r="N41">
-        <v>-7.017207679999999</v>
+        <v>-7.245084800000002</v>
       </c>
       <c r="O41">
-        <v>-1.2630973824</v>
+        <v>-1.304115264</v>
       </c>
       <c r="P41">
-        <v>-5.7541102976</v>
+        <v>-5.940969536000002</v>
       </c>
       <c r="Q41">
-        <v>-1.224110297599999</v>
+        <v>-1.410969536000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1408496517167474</v>
+        <v>0.1424338125786932</v>
       </c>
       <c r="T41">
-        <v>1.602673678327935</v>
+        <v>1.629384906300067</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03787466346234862</v>
+        <v>0.03692779687578989</v>
       </c>
       <c r="W41">
-        <v>0.2268691543555782</v>
+        <v>0.2270924254966888</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2104147970130479</v>
+        <v>0.2051544270877216</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1762972577458914</v>
+        <v>0.1781972577458914</v>
       </c>
       <c r="C42">
-        <v>13.4832703743643</v>
+        <v>11.99393950034142</v>
       </c>
       <c r="D42">
-        <v>36.43927037436431</v>
+        <v>35.91633950034142</v>
       </c>
       <c r="E42">
-        <v>31.31600000000001</v>
+        <v>32.28240000000001</v>
       </c>
       <c r="F42">
-        <v>38.65600000000001</v>
+        <v>39.62240000000001</v>
       </c>
       <c r="G42">
         <v>15.7</v>
@@ -4719,37 +4719,37 @@
         <v>1.87</v>
       </c>
       <c r="M42">
-        <v>9.115084800000002</v>
+        <v>9.342961920000002</v>
       </c>
       <c r="N42">
-        <v>-7.245084800000002</v>
+        <v>-7.472961920000002</v>
       </c>
       <c r="O42">
-        <v>-1.304115264</v>
+        <v>-1.3451331456</v>
       </c>
       <c r="P42">
-        <v>-5.940969536000002</v>
+        <v>-6.127828774400002</v>
       </c>
       <c r="Q42">
-        <v>-1.410969536000001</v>
+        <v>-1.597828774400002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1424338125786932</v>
+        <v>0.1440716738088405</v>
       </c>
       <c r="T42">
-        <v>1.629384906300067</v>
+        <v>1.657001599627187</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03692779687578989</v>
+        <v>0.03602711890320965</v>
       </c>
       <c r="W42">
-        <v>0.2270924254966888</v>
+        <v>0.2273048053626232</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2051544270877216</v>
+        <v>0.2001506605733869</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1781972577458914</v>
+        <v>0.1800972577458914</v>
       </c>
       <c r="C43">
-        <v>11.99393950034142</v>
+        <v>10.5194051854936</v>
       </c>
       <c r="D43">
-        <v>35.91633950034142</v>
+        <v>35.4082051854936</v>
       </c>
       <c r="E43">
-        <v>32.28240000000001</v>
+        <v>33.24880000000001</v>
       </c>
       <c r="F43">
-        <v>39.62240000000001</v>
+        <v>40.58880000000001</v>
       </c>
       <c r="G43">
         <v>15.7</v>
@@ -4801,37 +4801,37 @@
         <v>1.87</v>
       </c>
       <c r="M43">
-        <v>9.342961920000002</v>
+        <v>9.570839040000003</v>
       </c>
       <c r="N43">
-        <v>-7.472961920000002</v>
+        <v>-7.700839040000003</v>
       </c>
       <c r="O43">
-        <v>-1.3451331456</v>
+        <v>-1.3861510272</v>
       </c>
       <c r="P43">
-        <v>-6.127828774400002</v>
+        <v>-6.314688012800002</v>
       </c>
       <c r="Q43">
-        <v>-1.597828774400002</v>
+        <v>-1.784688012800002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1440716738088405</v>
+        <v>0.1457660130124412</v>
       </c>
       <c r="T43">
-        <v>1.657001599627187</v>
+        <v>1.685570592724207</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03602711890320965</v>
+        <v>0.03516933035789513</v>
       </c>
       <c r="W43">
-        <v>0.2273048053626232</v>
+        <v>0.2275070719016083</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2001506605733869</v>
+        <v>0.195385168654973</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1800972577458914</v>
+        <v>0.1819972577458914</v>
       </c>
       <c r="C44">
-        <v>10.51940518549362</v>
+        <v>9.059048178092212</v>
       </c>
       <c r="D44">
-        <v>35.40820518549361</v>
+        <v>34.91424817809221</v>
       </c>
       <c r="E44">
-        <v>33.2488</v>
+        <v>34.2152</v>
       </c>
       <c r="F44">
-        <v>40.5888</v>
+        <v>41.5552</v>
       </c>
       <c r="G44">
         <v>15.7</v>
@@ -4883,37 +4883,37 @@
         <v>1.87</v>
       </c>
       <c r="M44">
-        <v>9.570839040000001</v>
+        <v>9.79871616</v>
       </c>
       <c r="N44">
-        <v>-7.700839040000001</v>
+        <v>-7.92871616</v>
       </c>
       <c r="O44">
-        <v>-1.3861510272</v>
+        <v>-1.4271689088</v>
       </c>
       <c r="P44">
-        <v>-6.3146880128</v>
+        <v>-6.5015472512</v>
       </c>
       <c r="Q44">
-        <v>-1.7846880128</v>
+        <v>-1.9715472512</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1457660130124412</v>
+        <v>0.1475198027144139</v>
       </c>
       <c r="T44">
-        <v>1.685570592724207</v>
+        <v>1.715142006631649</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03516933035789514</v>
+        <v>0.03435143895422316</v>
       </c>
       <c r="W44">
-        <v>0.2275070719016083</v>
+        <v>0.2276999306945942</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.195385168654973</v>
+        <v>0.1908413275234621</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1819972577458914</v>
+        <v>0.1838972577458914</v>
       </c>
       <c r="C45">
-        <v>9.059048178092212</v>
+        <v>7.612283306108715</v>
       </c>
       <c r="D45">
-        <v>34.91424817809221</v>
+        <v>34.43388330610871</v>
       </c>
       <c r="E45">
-        <v>34.2152</v>
+        <v>35.1816</v>
       </c>
       <c r="F45">
-        <v>41.5552</v>
+        <v>42.5216</v>
       </c>
       <c r="G45">
         <v>15.7</v>
@@ -4965,37 +4965,37 @@
         <v>1.87</v>
       </c>
       <c r="M45">
-        <v>9.79871616</v>
+        <v>10.02659328</v>
       </c>
       <c r="N45">
-        <v>-7.92871616</v>
+        <v>-8.156593279999999</v>
       </c>
       <c r="O45">
-        <v>-1.4271689088</v>
+        <v>-1.4681867904</v>
       </c>
       <c r="P45">
-        <v>-6.5015472512</v>
+        <v>-6.688406489599999</v>
       </c>
       <c r="Q45">
-        <v>-1.9715472512</v>
+        <v>-2.158406489599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1475198027144139</v>
+        <v>0.1493362277628855</v>
       </c>
       <c r="T45">
-        <v>1.715142006631649</v>
+        <v>1.745769542464357</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03435143895422316</v>
+        <v>0.03357072443253627</v>
       </c>
       <c r="W45">
-        <v>0.2276999306945942</v>
+        <v>0.227884023178808</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1908413275234621</v>
+        <v>0.1865040246252017</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1838972577458914</v>
+        <v>0.1857972577458914</v>
       </c>
       <c r="C46">
-        <v>7.612283306108715</v>
+        <v>6.178557164618439</v>
       </c>
       <c r="D46">
-        <v>34.43388330610871</v>
+        <v>33.96655716461844</v>
       </c>
       <c r="E46">
-        <v>35.1816</v>
+        <v>36.148</v>
       </c>
       <c r="F46">
-        <v>42.5216</v>
+        <v>43.488</v>
       </c>
       <c r="G46">
         <v>15.7</v>
@@ -5047,37 +5047,37 @@
         <v>1.87</v>
       </c>
       <c r="M46">
-        <v>10.02659328</v>
+        <v>10.2544704</v>
       </c>
       <c r="N46">
-        <v>-8.156593279999999</v>
+        <v>-8.384470400000001</v>
       </c>
       <c r="O46">
-        <v>-1.4681867904</v>
+        <v>-1.509204672</v>
       </c>
       <c r="P46">
-        <v>-6.688406489599999</v>
+        <v>-6.875265728000001</v>
       </c>
       <c r="Q46">
-        <v>-2.158406489599999</v>
+        <v>-2.345265728000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1493362277628855</v>
+        <v>0.1512187046313016</v>
       </c>
       <c r="T46">
-        <v>1.745769542464357</v>
+        <v>1.7775108068728</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03357072443253627</v>
+        <v>0.03282470833403547</v>
       </c>
       <c r="W46">
-        <v>0.227884023178808</v>
+        <v>0.2280599337748344</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1865040246252017</v>
+        <v>0.1823594907446414</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1857972577458914</v>
+        <v>0.1876972577458914</v>
       </c>
       <c r="C47">
-        <v>6.178557164618439</v>
+        <v>4.757345988997663</v>
       </c>
       <c r="D47">
-        <v>33.96655716461844</v>
+        <v>33.51174598899766</v>
       </c>
       <c r="E47">
-        <v>36.148</v>
+        <v>37.1144</v>
       </c>
       <c r="F47">
-        <v>43.488</v>
+        <v>44.4544</v>
       </c>
       <c r="G47">
         <v>15.7</v>
@@ -5129,37 +5129,37 @@
         <v>1.87</v>
       </c>
       <c r="M47">
-        <v>10.2544704</v>
+        <v>10.48234752</v>
       </c>
       <c r="N47">
-        <v>-8.384470400000001</v>
+        <v>-8.61234752</v>
       </c>
       <c r="O47">
-        <v>-1.509204672</v>
+        <v>-1.5502225536</v>
       </c>
       <c r="P47">
-        <v>-6.875265728000001</v>
+        <v>-7.0621249664</v>
       </c>
       <c r="Q47">
-        <v>-2.345265728000001</v>
+        <v>-2.5321249664</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1512187046313016</v>
+        <v>0.1531709028652146</v>
       </c>
       <c r="T47">
-        <v>1.7775108068728</v>
+        <v>1.810427673666741</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03282470833403547</v>
+        <v>0.03211112771807817</v>
       </c>
       <c r="W47">
-        <v>0.2280599337748344</v>
+        <v>0.2282281960840772</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1823594907446414</v>
+        <v>0.1783951539893233</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1876972577458914</v>
+        <v>0.1895972577458914</v>
       </c>
       <c r="C48">
-        <v>4.757345988997663</v>
+        <v>3.34815369673008</v>
       </c>
       <c r="D48">
-        <v>33.51174598899766</v>
+        <v>33.06895369673008</v>
       </c>
       <c r="E48">
-        <v>37.1144</v>
+        <v>38.0808</v>
       </c>
       <c r="F48">
-        <v>44.4544</v>
+        <v>45.4208</v>
       </c>
       <c r="G48">
         <v>15.7</v>
@@ -5211,37 +5211,37 @@
         <v>1.87</v>
       </c>
       <c r="M48">
-        <v>10.48234752</v>
+        <v>10.71022464</v>
       </c>
       <c r="N48">
-        <v>-8.61234752</v>
+        <v>-8.840224639999999</v>
       </c>
       <c r="O48">
-        <v>-1.5502225536</v>
+        <v>-1.5912404352</v>
       </c>
       <c r="P48">
-        <v>-7.0621249664</v>
+        <v>-7.248984204799999</v>
       </c>
       <c r="Q48">
-        <v>-2.5321249664</v>
+        <v>-2.718984204799999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1531709028652146</v>
+        <v>0.1551967689570111</v>
       </c>
       <c r="T48">
-        <v>1.810427673666741</v>
+        <v>1.844586686377434</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03211112771807817</v>
+        <v>0.03142791223471481</v>
       </c>
       <c r="W48">
-        <v>0.2282281960840772</v>
+        <v>0.2283892982950542</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1783951539893233</v>
+        <v>0.1745995124150823</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1895972577458914</v>
+        <v>0.1914972577458914</v>
       </c>
       <c r="C49">
-        <v>3.34815369673008</v>
+        <v>1.950510082431094</v>
       </c>
       <c r="D49">
-        <v>33.06895369673008</v>
+        <v>32.6377100824311</v>
       </c>
       <c r="E49">
-        <v>38.0808</v>
+        <v>39.04720000000001</v>
       </c>
       <c r="F49">
-        <v>45.4208</v>
+        <v>46.38720000000001</v>
       </c>
       <c r="G49">
         <v>15.7</v>
@@ -5293,37 +5293,37 @@
         <v>1.87</v>
       </c>
       <c r="M49">
-        <v>10.71022464</v>
+        <v>10.93810176</v>
       </c>
       <c r="N49">
-        <v>-8.840224639999999</v>
+        <v>-9.068101760000001</v>
       </c>
       <c r="O49">
-        <v>-1.5912404352</v>
+        <v>-1.6322583168</v>
       </c>
       <c r="P49">
-        <v>-7.248984204799999</v>
+        <v>-7.435843443200001</v>
       </c>
       <c r="Q49">
-        <v>-2.718984204799999</v>
+        <v>-2.905843443200001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1551967689570111</v>
+        <v>0.1573005529754152</v>
       </c>
       <c r="T49">
-        <v>1.844586686377434</v>
+        <v>1.880059507269308</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03142791223471481</v>
+        <v>0.03077316406315824</v>
       </c>
       <c r="W49">
-        <v>0.2283892982950542</v>
+        <v>0.2285436879139073</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1745995124150823</v>
+        <v>0.1709620225731014</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1914972577458914</v>
+        <v>0.1933972577458914</v>
       </c>
       <c r="C50">
-        <v>1.950510082431101</v>
+        <v>0.5639691522833346</v>
       </c>
       <c r="D50">
-        <v>32.63771008243111</v>
+        <v>32.21756915228334</v>
       </c>
       <c r="E50">
-        <v>39.0472</v>
+        <v>40.0136</v>
       </c>
       <c r="F50">
-        <v>46.3872</v>
+        <v>47.3536</v>
       </c>
       <c r="G50">
         <v>15.7</v>
@@ -5375,37 +5375,37 @@
         <v>1.87</v>
       </c>
       <c r="M50">
-        <v>10.93810176</v>
+        <v>11.16597888</v>
       </c>
       <c r="N50">
-        <v>-9.068101760000001</v>
+        <v>-9.29597888</v>
       </c>
       <c r="O50">
-        <v>-1.6322583168</v>
+        <v>-1.6732761984</v>
       </c>
       <c r="P50">
-        <v>-7.435843443200001</v>
+        <v>-7.6227026816</v>
       </c>
       <c r="Q50">
-        <v>-2.905843443200001</v>
+        <v>-3.0927026816</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1573005529754152</v>
+        <v>0.1594868383278743</v>
       </c>
       <c r="T50">
-        <v>1.880059507269308</v>
+        <v>1.916923419176549</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03077316406315825</v>
+        <v>0.03014514030676726</v>
       </c>
       <c r="W50">
-        <v>0.2285436879139073</v>
+        <v>0.2286917759156643</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1709620225731013</v>
+        <v>0.1674730017042627</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1933972577458914</v>
+        <v>0.1952972577458914</v>
       </c>
       <c r="C51">
-        <v>0.5639691522833346</v>
+        <v>-0.811892414519356</v>
       </c>
       <c r="D51">
-        <v>32.21756915228334</v>
+        <v>31.80810758548064</v>
       </c>
       <c r="E51">
-        <v>40.0136</v>
+        <v>40.98</v>
       </c>
       <c r="F51">
-        <v>47.3536</v>
+        <v>48.32</v>
       </c>
       <c r="G51">
         <v>15.7</v>
@@ -5457,37 +5457,37 @@
         <v>1.87</v>
       </c>
       <c r="M51">
-        <v>11.16597888</v>
+        <v>11.393856</v>
       </c>
       <c r="N51">
-        <v>-9.29597888</v>
+        <v>-9.523856000000002</v>
       </c>
       <c r="O51">
-        <v>-1.6732761984</v>
+        <v>-1.71429408</v>
       </c>
       <c r="P51">
-        <v>-7.6227026816</v>
+        <v>-7.809561920000002</v>
       </c>
       <c r="Q51">
-        <v>-3.0927026816</v>
+        <v>-3.279561920000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1594868383278743</v>
+        <v>0.1617605750944318</v>
       </c>
       <c r="T51">
-        <v>1.916923419176549</v>
+        <v>1.95526188756008</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03014514030676726</v>
+        <v>0.02954223750063192</v>
       </c>
       <c r="W51">
-        <v>0.2286917759156643</v>
+        <v>0.228833940397351</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1674730017042627</v>
+        <v>0.1641235416701773</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1952972577458914</v>
+        <v>0.1971972577458914</v>
       </c>
       <c r="C52">
-        <v>-0.811892414519356</v>
+        <v>-2.177476688476617</v>
       </c>
       <c r="D52">
-        <v>31.80810758548064</v>
+        <v>31.40892331152339</v>
       </c>
       <c r="E52">
-        <v>40.98</v>
+        <v>41.9464</v>
       </c>
       <c r="F52">
-        <v>48.32</v>
+        <v>49.2864</v>
       </c>
       <c r="G52">
         <v>15.7</v>
@@ -5539,37 +5539,37 @@
         <v>1.87</v>
       </c>
       <c r="M52">
-        <v>11.393856</v>
+        <v>11.62173312</v>
       </c>
       <c r="N52">
-        <v>-9.523856000000002</v>
+        <v>-9.751733120000001</v>
       </c>
       <c r="O52">
-        <v>-1.71429408</v>
+        <v>-1.7553119616</v>
       </c>
       <c r="P52">
-        <v>-7.809561920000002</v>
+        <v>-7.9964211584</v>
       </c>
       <c r="Q52">
-        <v>-3.279561920000002</v>
+        <v>-3.4664211584</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1617605750944318</v>
+        <v>0.1641271174432977</v>
       </c>
       <c r="T52">
-        <v>1.95526188756008</v>
+        <v>1.995165191387837</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02954223750063192</v>
+        <v>0.028962977941796</v>
       </c>
       <c r="W52">
-        <v>0.228833940397351</v>
+        <v>0.2289705298013245</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1641235416701773</v>
+        <v>0.1609054330099777</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1971972577458914</v>
+        <v>0.1990972577458914</v>
       </c>
       <c r="C53">
-        <v>-2.177476688476617</v>
+        <v>-3.533165806686519</v>
       </c>
       <c r="D53">
-        <v>31.40892331152339</v>
+        <v>31.01963419331348</v>
       </c>
       <c r="E53">
-        <v>41.9464</v>
+        <v>42.9128</v>
       </c>
       <c r="F53">
-        <v>49.2864</v>
+        <v>50.2528</v>
       </c>
       <c r="G53">
         <v>15.7</v>
@@ -5621,37 +5621,37 @@
         <v>1.87</v>
       </c>
       <c r="M53">
-        <v>11.62173312</v>
+        <v>11.84961024</v>
       </c>
       <c r="N53">
-        <v>-9.751733120000001</v>
+        <v>-9.97961024</v>
       </c>
       <c r="O53">
-        <v>-1.7553119616</v>
+        <v>-1.7963298432</v>
       </c>
       <c r="P53">
-        <v>-7.9964211584</v>
+        <v>-8.183280396799999</v>
       </c>
       <c r="Q53">
-        <v>-3.4664211584</v>
+        <v>-3.653280396799999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1641271174432977</v>
+        <v>0.1665922657233665</v>
       </c>
       <c r="T53">
-        <v>1.995165191387837</v>
+        <v>2.036731132875084</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.028962977941796</v>
+        <v>0.02840599759676146</v>
       </c>
       <c r="W53">
-        <v>0.2289705298013245</v>
+        <v>0.2291018657666837</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1609054330099777</v>
+        <v>0.157811097759786</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1990972577458914</v>
+        <v>0.2009972577458914</v>
       </c>
       <c r="C54">
-        <v>-3.533165806686519</v>
+        <v>-4.87932319301737</v>
       </c>
       <c r="D54">
-        <v>31.01963419331348</v>
+        <v>30.63987680698263</v>
       </c>
       <c r="E54">
-        <v>42.9128</v>
+        <v>43.8792</v>
       </c>
       <c r="F54">
-        <v>50.2528</v>
+        <v>51.2192</v>
       </c>
       <c r="G54">
         <v>15.7</v>
@@ -5703,37 +5703,37 @@
         <v>1.87</v>
       </c>
       <c r="M54">
-        <v>11.84961024</v>
+        <v>12.07748736</v>
       </c>
       <c r="N54">
-        <v>-9.97961024</v>
+        <v>-10.20748736</v>
       </c>
       <c r="O54">
-        <v>-1.7963298432</v>
+        <v>-1.8373477248</v>
       </c>
       <c r="P54">
-        <v>-8.183280396799999</v>
+        <v>-8.370139635200001</v>
       </c>
       <c r="Q54">
-        <v>-3.653280396799999</v>
+        <v>-3.840139635200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1665922657233665</v>
+        <v>0.1691623139302466</v>
       </c>
       <c r="T54">
-        <v>2.036731132875084</v>
+        <v>2.080065837829873</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02840599759676146</v>
+        <v>0.02787003537795464</v>
       </c>
       <c r="W54">
-        <v>0.2291018657666837</v>
+        <v>0.2292282456578783</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.157811097759786</v>
+        <v>0.1548335298775257</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2009972577458914</v>
+        <v>0.2028972577458914</v>
       </c>
       <c r="C55">
-        <v>-4.87932319301737</v>
+        <v>-6.216294689735868</v>
       </c>
       <c r="D55">
-        <v>30.63987680698263</v>
+        <v>30.26930531026413</v>
       </c>
       <c r="E55">
-        <v>43.8792</v>
+        <v>44.8456</v>
       </c>
       <c r="F55">
-        <v>51.2192</v>
+        <v>52.1856</v>
       </c>
       <c r="G55">
         <v>15.7</v>
@@ -5785,37 +5785,37 @@
         <v>1.87</v>
       </c>
       <c r="M55">
-        <v>12.07748736</v>
+        <v>12.30536448</v>
       </c>
       <c r="N55">
-        <v>-10.20748736</v>
+        <v>-10.43536448</v>
       </c>
       <c r="O55">
-        <v>-1.8373477248</v>
+        <v>-1.8783656064</v>
       </c>
       <c r="P55">
-        <v>-8.370139635200001</v>
+        <v>-8.556998873600001</v>
       </c>
       <c r="Q55">
-        <v>-3.840139635200001</v>
+        <v>-4.026998873600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1691623139302466</v>
+        <v>0.1718441033635128</v>
       </c>
       <c r="T55">
-        <v>2.080065837829873</v>
+        <v>2.125284660391392</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02787003537795464</v>
+        <v>0.02735392361169622</v>
       </c>
       <c r="W55">
-        <v>0.2292282456578783</v>
+        <v>0.229349944812362</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1548335298775257</v>
+        <v>0.1519662422872013</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2028972577458914</v>
+        <v>0.2047972577458914</v>
       </c>
       <c r="C56">
-        <v>-6.216294689735868</v>
+        <v>-7.544409607998283</v>
       </c>
       <c r="D56">
-        <v>30.26930531026413</v>
+        <v>29.90759039200172</v>
       </c>
       <c r="E56">
-        <v>44.8456</v>
+        <v>45.81200000000001</v>
       </c>
       <c r="F56">
-        <v>52.1856</v>
+        <v>53.15200000000001</v>
       </c>
       <c r="G56">
         <v>15.7</v>
@@ -5867,37 +5867,37 @@
         <v>1.87</v>
       </c>
       <c r="M56">
-        <v>12.30536448</v>
+        <v>12.5332416</v>
       </c>
       <c r="N56">
-        <v>-10.43536448</v>
+        <v>-10.6632416</v>
       </c>
       <c r="O56">
-        <v>-1.8783656064</v>
+        <v>-1.919383488</v>
       </c>
       <c r="P56">
-        <v>-8.556998873600001</v>
+        <v>-8.743858112000002</v>
       </c>
       <c r="Q56">
-        <v>-4.026998873600001</v>
+        <v>-4.213858112000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1718441033635128</v>
+        <v>0.1746450834382576</v>
       </c>
       <c r="T56">
-        <v>2.125284660391392</v>
+        <v>2.172513208400089</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02735392361169622</v>
+        <v>0.02685657954602902</v>
       </c>
       <c r="W56">
-        <v>0.229349944812362</v>
+        <v>0.2294672185430464</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1519662422872013</v>
+        <v>0.1492032197001611</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2047972577458914</v>
+        <v>0.2066972577458914</v>
       </c>
       <c r="C57">
-        <v>-7.544409607998283</v>
+        <v>-8.863981703911492</v>
       </c>
       <c r="D57">
-        <v>29.90759039200172</v>
+        <v>29.55441829608852</v>
       </c>
       <c r="E57">
-        <v>45.81200000000001</v>
+        <v>46.77840000000001</v>
       </c>
       <c r="F57">
-        <v>53.15200000000001</v>
+        <v>54.11840000000001</v>
       </c>
       <c r="G57">
         <v>15.7</v>
@@ -5949,37 +5949,37 @@
         <v>1.87</v>
       </c>
       <c r="M57">
-        <v>12.5332416</v>
+        <v>12.76111872</v>
       </c>
       <c r="N57">
-        <v>-10.6632416</v>
+        <v>-10.89111872</v>
       </c>
       <c r="O57">
-        <v>-1.919383488</v>
+        <v>-1.9604013696</v>
       </c>
       <c r="P57">
-        <v>-8.743858112000002</v>
+        <v>-8.930717350400002</v>
       </c>
       <c r="Q57">
-        <v>-4.213858112000001</v>
+        <v>-4.400717350400002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1746450834382576</v>
+        <v>0.1775733807891271</v>
       </c>
       <c r="T57">
-        <v>2.172513208400089</v>
+        <v>2.221888508591</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02685657954602902</v>
+        <v>0.02637699776842135</v>
       </c>
       <c r="W57">
-        <v>0.2294672185430464</v>
+        <v>0.2295803039262062</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1492032197001611</v>
+        <v>0.1465388764912298</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2066972577458914</v>
+        <v>0.2085972577458914</v>
       </c>
       <c r="C58">
-        <v>-8.863981703911492</v>
+        <v>-10.17531008624467</v>
       </c>
       <c r="D58">
-        <v>29.55441829608852</v>
+        <v>29.20948991375533</v>
       </c>
       <c r="E58">
-        <v>46.77840000000001</v>
+        <v>47.74480000000001</v>
       </c>
       <c r="F58">
-        <v>54.11840000000001</v>
+        <v>55.08480000000001</v>
       </c>
       <c r="G58">
         <v>15.7</v>
@@ -6031,37 +6031,37 @@
         <v>1.87</v>
       </c>
       <c r="M58">
-        <v>12.76111872</v>
+        <v>12.98899584</v>
       </c>
       <c r="N58">
-        <v>-10.89111872</v>
+        <v>-11.11899584</v>
       </c>
       <c r="O58">
-        <v>-1.9604013696</v>
+        <v>-2.001419251200001</v>
       </c>
       <c r="P58">
-        <v>-8.930717350400002</v>
+        <v>-9.117576588800002</v>
       </c>
       <c r="Q58">
-        <v>-4.400717350400002</v>
+        <v>-4.587576588800002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1775733807891271</v>
+        <v>0.1806378780167812</v>
       </c>
       <c r="T58">
-        <v>2.221888508591</v>
+        <v>2.273560334372187</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02637699776842135</v>
+        <v>0.02591424342160694</v>
       </c>
       <c r="W58">
-        <v>0.2295803039262062</v>
+        <v>0.2296894214011851</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1465388764912298</v>
+        <v>0.1439680190089274</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2085972577458914</v>
+        <v>0.2104972577458914</v>
       </c>
       <c r="C59">
-        <v>-10.17531008624467</v>
+        <v>-11.47868006131105</v>
       </c>
       <c r="D59">
-        <v>29.20948991375533</v>
+        <v>28.87251993868896</v>
       </c>
       <c r="E59">
-        <v>47.74480000000001</v>
+        <v>48.71120000000001</v>
       </c>
       <c r="F59">
-        <v>55.08480000000001</v>
+        <v>56.05120000000001</v>
       </c>
       <c r="G59">
         <v>15.7</v>
@@ -6113,37 +6113,37 @@
         <v>1.87</v>
       </c>
       <c r="M59">
-        <v>12.98899584</v>
+        <v>13.21687296</v>
       </c>
       <c r="N59">
-        <v>-11.11899584</v>
+        <v>-11.34687296</v>
       </c>
       <c r="O59">
-        <v>-2.001419251200001</v>
+        <v>-2.0424371328</v>
       </c>
       <c r="P59">
-        <v>-9.117576588800002</v>
+        <v>-9.304435827200003</v>
       </c>
       <c r="Q59">
-        <v>-4.587576588800002</v>
+        <v>-4.774435827200002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1806378780167812</v>
+        <v>0.1838483036838474</v>
       </c>
       <c r="T59">
-        <v>2.273560334372187</v>
+        <v>2.32769272328581</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02591424342160694</v>
+        <v>0.02546744612123441</v>
       </c>
       <c r="W59">
-        <v>0.2296894214011851</v>
+        <v>0.2297947762046129</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1439680190089274</v>
+        <v>0.1414858117846357</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2104972577458914</v>
+        <v>0.2123972577458914</v>
       </c>
       <c r="C60">
-        <v>-11.47868006131104</v>
+        <v>-12.77436392003567</v>
       </c>
       <c r="D60">
-        <v>28.87251993868896</v>
+        <v>28.54323607996433</v>
       </c>
       <c r="E60">
-        <v>48.7112</v>
+        <v>49.6776</v>
       </c>
       <c r="F60">
-        <v>56.05119999999999</v>
+        <v>57.01759999999999</v>
       </c>
       <c r="G60">
         <v>15.7</v>
@@ -6195,37 +6195,37 @@
         <v>1.87</v>
       </c>
       <c r="M60">
-        <v>13.21687296</v>
+        <v>13.44475008</v>
       </c>
       <c r="N60">
-        <v>-11.34687296</v>
+        <v>-11.57475008</v>
       </c>
       <c r="O60">
-        <v>-2.0424371328</v>
+        <v>-2.0834550144</v>
       </c>
       <c r="P60">
-        <v>-9.304435827199999</v>
+        <v>-9.491295065599997</v>
       </c>
       <c r="Q60">
-        <v>-4.774435827199999</v>
+        <v>-4.961295065599997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1838483036838474</v>
+        <v>0.1872153354810143</v>
       </c>
       <c r="T60">
-        <v>2.32769272328581</v>
+        <v>2.384465716536682</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02546744612123442</v>
+        <v>0.02503579449206095</v>
       </c>
       <c r="W60">
-        <v>0.2297947762046129</v>
+        <v>0.229896559658772</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1414858117846357</v>
+        <v>0.1390877471781164</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2123972577458914</v>
+        <v>0.2142972577458914</v>
       </c>
       <c r="C61">
-        <v>-12.77436392003567</v>
+        <v>-14.06262167177261</v>
       </c>
       <c r="D61">
-        <v>28.54323607996433</v>
+        <v>28.22137832822738</v>
       </c>
       <c r="E61">
-        <v>49.6776</v>
+        <v>50.644</v>
       </c>
       <c r="F61">
-        <v>57.01759999999999</v>
+        <v>57.98399999999999</v>
       </c>
       <c r="G61">
         <v>15.7</v>
@@ -6277,37 +6277,37 @@
         <v>1.87</v>
       </c>
       <c r="M61">
-        <v>13.44475008</v>
+        <v>13.6726272</v>
       </c>
       <c r="N61">
-        <v>-11.57475008</v>
+        <v>-11.8026272</v>
       </c>
       <c r="O61">
-        <v>-2.0834550144</v>
+        <v>-2.124472896</v>
       </c>
       <c r="P61">
-        <v>-9.491295065599997</v>
+        <v>-9.678154304</v>
       </c>
       <c r="Q61">
-        <v>-4.961295065599997</v>
+        <v>-5.148154303999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1872153354810143</v>
+        <v>0.1907507188680397</v>
       </c>
       <c r="T61">
-        <v>2.384465716536682</v>
+        <v>2.4440773594501</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02503579449206095</v>
+        <v>0.0246185312505266</v>
       </c>
       <c r="W61">
-        <v>0.229896559658772</v>
+        <v>0.2299949503311258</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1390877471781164</v>
+        <v>0.1367696180584811</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2142972577458914</v>
+        <v>0.2161972577458914</v>
       </c>
       <c r="C62">
-        <v>-14.06262167177261</v>
+        <v>-15.34370172902798</v>
       </c>
       <c r="D62">
-        <v>28.22137832822738</v>
+        <v>27.90669827097203</v>
       </c>
       <c r="E62">
-        <v>50.644</v>
+        <v>51.61040000000001</v>
       </c>
       <c r="F62">
-        <v>57.98399999999999</v>
+        <v>58.9504</v>
       </c>
       <c r="G62">
         <v>15.7</v>
@@ -6359,37 +6359,37 @@
         <v>1.87</v>
       </c>
       <c r="M62">
-        <v>13.6726272</v>
+        <v>13.90050432</v>
       </c>
       <c r="N62">
-        <v>-11.8026272</v>
+        <v>-12.03050432</v>
       </c>
       <c r="O62">
-        <v>-2.124472896</v>
+        <v>-2.1654907776</v>
       </c>
       <c r="P62">
-        <v>-9.678154304</v>
+        <v>-9.865013542400002</v>
       </c>
       <c r="Q62">
-        <v>-5.148154303999999</v>
+        <v>-5.335013542400001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1907507188680397</v>
+        <v>0.1944674039672203</v>
       </c>
       <c r="T62">
-        <v>2.4440773594501</v>
+        <v>2.506746009692411</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0246185312505266</v>
+        <v>0.02421494877100977</v>
       </c>
       <c r="W62">
-        <v>0.2299949503311258</v>
+        <v>0.2300901150797959</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1367696180584811</v>
+        <v>0.1345274931722764</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2161972577458914</v>
+        <v>0.2180972577458914</v>
       </c>
       <c r="C63">
-        <v>-15.34370172902798</v>
+        <v>-16.61784154687839</v>
       </c>
       <c r="D63">
-        <v>27.90669827097203</v>
+        <v>27.59895845312161</v>
       </c>
       <c r="E63">
-        <v>51.61040000000001</v>
+        <v>52.57680000000001</v>
       </c>
       <c r="F63">
-        <v>58.9504</v>
+        <v>59.9168</v>
       </c>
       <c r="G63">
         <v>15.7</v>
@@ -6441,37 +6441,37 @@
         <v>1.87</v>
       </c>
       <c r="M63">
-        <v>13.90050432</v>
+        <v>14.12838144</v>
       </c>
       <c r="N63">
-        <v>-12.03050432</v>
+        <v>-12.25838144</v>
       </c>
       <c r="O63">
-        <v>-2.1654907776</v>
+        <v>-2.2065086592</v>
       </c>
       <c r="P63">
-        <v>-9.865013542400002</v>
+        <v>-10.0518727808</v>
       </c>
       <c r="Q63">
-        <v>-5.335013542400001</v>
+        <v>-5.5218727808</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1944674039672203</v>
+        <v>0.1983797040716208</v>
       </c>
       <c r="T63">
-        <v>2.506746009692411</v>
+        <v>2.572713009947474</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02421494877100977</v>
+        <v>0.02382438508115477</v>
       </c>
       <c r="W63">
-        <v>0.2300901150797959</v>
+        <v>0.2301822099978637</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1345274931722764</v>
+        <v>0.1323576948953044</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2180972577458914</v>
+        <v>0.2199972577458914</v>
       </c>
       <c r="C64">
-        <v>-16.61784154687839</v>
+        <v>-17.88526822054408</v>
       </c>
       <c r="D64">
-        <v>27.59895845312161</v>
+        <v>27.29793177945593</v>
       </c>
       <c r="E64">
-        <v>52.57680000000001</v>
+        <v>53.54320000000001</v>
       </c>
       <c r="F64">
-        <v>59.9168</v>
+        <v>60.8832</v>
       </c>
       <c r="G64">
         <v>15.7</v>
@@ -6523,37 +6523,37 @@
         <v>1.87</v>
       </c>
       <c r="M64">
-        <v>14.12838144</v>
+        <v>14.35625856</v>
       </c>
       <c r="N64">
-        <v>-12.25838144</v>
+        <v>-12.48625856</v>
       </c>
       <c r="O64">
-        <v>-2.2065086592</v>
+        <v>-2.2475265408</v>
       </c>
       <c r="P64">
-        <v>-10.0518727808</v>
+        <v>-10.2387320192</v>
       </c>
       <c r="Q64">
-        <v>-5.5218727808</v>
+        <v>-5.7087320192</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1983797040716208</v>
+        <v>0.2025034798573403</v>
       </c>
       <c r="T64">
-        <v>2.572713009947474</v>
+        <v>2.642245794000108</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02382438508115477</v>
+        <v>0.02344622023859676</v>
       </c>
       <c r="W64">
-        <v>0.2301822099978637</v>
+        <v>0.2302713812677389</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1323576948953044</v>
+        <v>0.1302567791033155</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2199972577458914</v>
+        <v>0.2218972577458914</v>
       </c>
       <c r="C65">
-        <v>-17.88526822054408</v>
+        <v>-19.14619904427678</v>
       </c>
       <c r="D65">
-        <v>27.29793177945593</v>
+        <v>27.00340095572323</v>
       </c>
       <c r="E65">
-        <v>53.54320000000001</v>
+        <v>54.50960000000001</v>
       </c>
       <c r="F65">
-        <v>60.8832</v>
+        <v>61.8496</v>
       </c>
       <c r="G65">
         <v>15.7</v>
@@ -6605,37 +6605,37 @@
         <v>1.87</v>
       </c>
       <c r="M65">
-        <v>14.35625856</v>
+        <v>14.58413568</v>
       </c>
       <c r="N65">
-        <v>-12.48625856</v>
+        <v>-12.71413568</v>
       </c>
       <c r="O65">
-        <v>-2.2475265408</v>
+        <v>-2.2885444224</v>
       </c>
       <c r="P65">
-        <v>-10.2387320192</v>
+        <v>-10.4255912576</v>
       </c>
       <c r="Q65">
-        <v>-5.7087320192</v>
+        <v>-5.8955912576</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2025034798573403</v>
+        <v>0.206856354297822</v>
       </c>
       <c r="T65">
-        <v>2.642245794000108</v>
+        <v>2.715641510500112</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02344622023859676</v>
+        <v>0.02307987304736869</v>
       </c>
       <c r="W65">
-        <v>0.2302713812677389</v>
+        <v>0.2303577659354305</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1302567791033155</v>
+        <v>0.128221516929826</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2218972577458914</v>
+        <v>0.2237972577458914</v>
       </c>
       <c r="C66">
-        <v>-19.14619904427678</v>
+        <v>-20.40084203445318</v>
       </c>
       <c r="D66">
-        <v>27.00340095572323</v>
+        <v>26.71515796554683</v>
       </c>
       <c r="E66">
-        <v>54.50960000000001</v>
+        <v>55.47600000000001</v>
       </c>
       <c r="F66">
-        <v>61.8496</v>
+        <v>62.816</v>
       </c>
       <c r="G66">
         <v>15.7</v>
@@ -6687,37 +6687,37 @@
         <v>1.87</v>
       </c>
       <c r="M66">
-        <v>14.58413568</v>
+        <v>14.8120128</v>
       </c>
       <c r="N66">
-        <v>-12.71413568</v>
+        <v>-12.9420128</v>
       </c>
       <c r="O66">
-        <v>-2.2885444224</v>
+        <v>-2.329562304</v>
       </c>
       <c r="P66">
-        <v>-10.4255912576</v>
+        <v>-10.612450496</v>
       </c>
       <c r="Q66">
-        <v>-5.8955912576</v>
+        <v>-6.082450496000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.206856354297822</v>
+        <v>0.2114579644206169</v>
       </c>
       <c r="T66">
-        <v>2.715641510500112</v>
+        <v>2.793231267942972</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02307987304736869</v>
+        <v>0.02272479807740917</v>
       </c>
       <c r="W66">
-        <v>0.2303577659354305</v>
+        <v>0.2304414926133469</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.128221516929826</v>
+        <v>0.1262488782078288</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2237972577458914</v>
+        <v>0.2256972577458914</v>
       </c>
       <c r="C67">
-        <v>-20.40084203445318</v>
+        <v>-21.64939641952021</v>
       </c>
       <c r="D67">
-        <v>26.71515796554683</v>
+        <v>26.43300358047979</v>
       </c>
       <c r="E67">
-        <v>55.47600000000001</v>
+        <v>56.44240000000001</v>
       </c>
       <c r="F67">
-        <v>62.816</v>
+        <v>63.7824</v>
       </c>
       <c r="G67">
         <v>15.7</v>
@@ -6769,37 +6769,37 @@
         <v>1.87</v>
       </c>
       <c r="M67">
-        <v>14.8120128</v>
+        <v>15.03988992</v>
       </c>
       <c r="N67">
-        <v>-12.9420128</v>
+        <v>-13.16988992</v>
       </c>
       <c r="O67">
-        <v>-2.329562304</v>
+        <v>-2.370580185600001</v>
       </c>
       <c r="P67">
-        <v>-10.612450496</v>
+        <v>-10.7993097344</v>
       </c>
       <c r="Q67">
-        <v>-6.082450496000001</v>
+        <v>-6.269309734400001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2114579644206169</v>
+        <v>0.2163302574918115</v>
       </c>
       <c r="T67">
-        <v>2.793231267942972</v>
+        <v>2.875385128764824</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02272479807740917</v>
+        <v>0.02238048295502418</v>
       </c>
       <c r="W67">
-        <v>0.2304414926133469</v>
+        <v>0.2305226821192053</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1262488782078288</v>
+        <v>0.1243360164168009</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2256972577458914</v>
+        <v>0.2275972577458914</v>
       </c>
       <c r="C68">
-        <v>-21.64939641952021</v>
+        <v>-22.89205309921728</v>
       </c>
       <c r="D68">
-        <v>26.43300358047979</v>
+        <v>26.15674690078272</v>
       </c>
       <c r="E68">
-        <v>56.44240000000001</v>
+        <v>57.40880000000001</v>
       </c>
       <c r="F68">
-        <v>63.7824</v>
+        <v>64.7488</v>
       </c>
       <c r="G68">
         <v>15.7</v>
@@ -6851,37 +6851,37 @@
         <v>1.87</v>
       </c>
       <c r="M68">
-        <v>15.03988992</v>
+        <v>15.26776704</v>
       </c>
       <c r="N68">
-        <v>-13.16988992</v>
+        <v>-13.39776704</v>
       </c>
       <c r="O68">
-        <v>-2.370580185600001</v>
+        <v>-2.4115980672</v>
       </c>
       <c r="P68">
-        <v>-10.7993097344</v>
+        <v>-10.9861689728</v>
       </c>
       <c r="Q68">
-        <v>-6.269309734400001</v>
+        <v>-6.456168972800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2163302574918115</v>
+        <v>0.2214978410521694</v>
       </c>
       <c r="T68">
-        <v>2.875385128764824</v>
+        <v>2.962518011454667</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02238048295502418</v>
+        <v>0.02204644589599397</v>
       </c>
       <c r="W68">
-        <v>0.2305226821192053</v>
+        <v>0.2306014480577246</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1243360164168009</v>
+        <v>0.1224802549777442</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2275972577458914</v>
+        <v>0.2294972577458914</v>
       </c>
       <c r="C69">
-        <v>-22.89205309921728</v>
+        <v>-24.12899507529966</v>
       </c>
       <c r="D69">
-        <v>26.15674690078272</v>
+        <v>25.88620492470035</v>
       </c>
       <c r="E69">
-        <v>57.40880000000001</v>
+        <v>58.37520000000001</v>
       </c>
       <c r="F69">
-        <v>64.7488</v>
+        <v>65.71520000000001</v>
       </c>
       <c r="G69">
         <v>15.7</v>
@@ -6933,37 +6933,37 @@
         <v>1.87</v>
       </c>
       <c r="M69">
-        <v>15.26776704</v>
+        <v>15.49564416</v>
       </c>
       <c r="N69">
-        <v>-13.39776704</v>
+        <v>-13.62564416</v>
       </c>
       <c r="O69">
-        <v>-2.4115980672</v>
+        <v>-2.452615948800001</v>
       </c>
       <c r="P69">
-        <v>-10.9861689728</v>
+        <v>-11.1730282112</v>
       </c>
       <c r="Q69">
-        <v>-6.456168972800001</v>
+        <v>-6.643028211200003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2214978410521694</v>
+        <v>0.2269883985850497</v>
       </c>
       <c r="T69">
-        <v>2.962518011454667</v>
+        <v>3.055096699312626</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02204644589599397</v>
+        <v>0.021722233456347</v>
       </c>
       <c r="W69">
-        <v>0.2306014480577246</v>
+        <v>0.2306778973509934</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1224802549777442</v>
+        <v>0.1206790747574833</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2294972577458914</v>
+        <v>0.2313972577458914</v>
       </c>
       <c r="C70">
-        <v>-24.12899507529966</v>
+        <v>-25.36039785580554</v>
       </c>
       <c r="D70">
-        <v>25.88620492470035</v>
+        <v>25.62120214419446</v>
       </c>
       <c r="E70">
-        <v>58.37520000000001</v>
+        <v>59.34160000000001</v>
       </c>
       <c r="F70">
-        <v>65.71520000000001</v>
+        <v>66.6816</v>
       </c>
       <c r="G70">
         <v>15.7</v>
@@ -7015,37 +7015,37 @@
         <v>1.87</v>
       </c>
       <c r="M70">
-        <v>15.49564416</v>
+        <v>15.72352128</v>
       </c>
       <c r="N70">
-        <v>-13.62564416</v>
+        <v>-13.85352128</v>
       </c>
       <c r="O70">
-        <v>-2.452615948800001</v>
+        <v>-2.4936338304</v>
       </c>
       <c r="P70">
-        <v>-11.1730282112</v>
+        <v>-11.3598874496</v>
       </c>
       <c r="Q70">
-        <v>-6.643028211200003</v>
+        <v>-6.829887449600002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2269883985850497</v>
+        <v>0.2328331856361804</v>
       </c>
       <c r="T70">
-        <v>3.055096699312626</v>
+        <v>3.153648205742066</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.021722233456347</v>
+        <v>0.02140741847871878</v>
       </c>
       <c r="W70">
-        <v>0.2306778973509934</v>
+        <v>0.2307521307227181</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1206790747574833</v>
+        <v>0.1189301026595487</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2313972577458914</v>
+        <v>0.2332972577458914</v>
       </c>
       <c r="C71">
-        <v>-25.36039785580554</v>
+        <v>-26.58642983474333</v>
       </c>
       <c r="D71">
-        <v>25.62120214419446</v>
+        <v>25.36157016525668</v>
       </c>
       <c r="E71">
-        <v>59.34160000000001</v>
+        <v>60.30800000000001</v>
       </c>
       <c r="F71">
-        <v>66.6816</v>
+        <v>67.64800000000001</v>
       </c>
       <c r="G71">
         <v>15.7</v>
@@ -7097,37 +7097,37 @@
         <v>1.87</v>
       </c>
       <c r="M71">
-        <v>15.72352128</v>
+        <v>15.9513984</v>
       </c>
       <c r="N71">
-        <v>-13.85352128</v>
+        <v>-14.0813984</v>
       </c>
       <c r="O71">
-        <v>-2.4936338304</v>
+        <v>-2.534651712000001</v>
       </c>
       <c r="P71">
-        <v>-11.3598874496</v>
+        <v>-11.546746688</v>
       </c>
       <c r="Q71">
-        <v>-6.829887449600002</v>
+        <v>-7.016746688000004</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2328331856361804</v>
+        <v>0.2390676251573864</v>
       </c>
       <c r="T71">
-        <v>3.153648205742066</v>
+        <v>3.258769812600134</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02140741847871878</v>
+        <v>0.02110159821473708</v>
       </c>
       <c r="W71">
-        <v>0.2307521307227181</v>
+        <v>0.230824243140965</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1189301026595487</v>
+        <v>0.1172311011929837</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2332972577458914</v>
+        <v>0.2351972577458915</v>
       </c>
       <c r="C72">
-        <v>-26.58642983474333</v>
+        <v>-27.80725264892492</v>
       </c>
       <c r="D72">
-        <v>25.36157016525668</v>
+        <v>25.10714735107509</v>
       </c>
       <c r="E72">
-        <v>60.30800000000001</v>
+        <v>61.27440000000001</v>
       </c>
       <c r="F72">
-        <v>67.64800000000001</v>
+        <v>68.6144</v>
       </c>
       <c r="G72">
         <v>15.7</v>
@@ -7179,37 +7179,37 @@
         <v>1.87</v>
       </c>
       <c r="M72">
-        <v>15.9513984</v>
+        <v>16.17927552</v>
       </c>
       <c r="N72">
-        <v>-14.0813984</v>
+        <v>-14.30927552</v>
       </c>
       <c r="O72">
-        <v>-2.534651712000001</v>
+        <v>-2.5756695936</v>
       </c>
       <c r="P72">
-        <v>-11.546746688</v>
+        <v>-11.7336059264</v>
       </c>
       <c r="Q72">
-        <v>-7.016746688000004</v>
+        <v>-7.203605926399999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2390676251573864</v>
+        <v>0.2457320260248825</v>
       </c>
       <c r="T72">
-        <v>3.258769812600134</v>
+        <v>3.371141185448415</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02110159821473708</v>
+        <v>0.02080439260607882</v>
       </c>
       <c r="W72">
-        <v>0.230824243140965</v>
+        <v>0.2308943242234866</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1172311011929837</v>
+        <v>0.1155799589226602</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2351972577458914</v>
+        <v>0.2370972577458914</v>
       </c>
       <c r="C73">
-        <v>-27.80725264892492</v>
+        <v>-29.02302151353461</v>
       </c>
       <c r="D73">
-        <v>25.10714735107509</v>
+        <v>24.85777848646539</v>
       </c>
       <c r="E73">
-        <v>61.27440000000001</v>
+        <v>62.2408</v>
       </c>
       <c r="F73">
-        <v>68.6144</v>
+        <v>69.5808</v>
       </c>
       <c r="G73">
         <v>15.7</v>
@@ -7261,37 +7261,37 @@
         <v>1.87</v>
       </c>
       <c r="M73">
-        <v>16.17927552</v>
+        <v>16.40715264</v>
       </c>
       <c r="N73">
-        <v>-14.30927552</v>
+        <v>-14.53715264</v>
       </c>
       <c r="O73">
-        <v>-2.5756695936</v>
+        <v>-2.6166874752</v>
       </c>
       <c r="P73">
-        <v>-11.7336059264</v>
+        <v>-11.9204651648</v>
       </c>
       <c r="Q73">
-        <v>-7.203605926399999</v>
+        <v>-7.390465164799999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2457320260248824</v>
+        <v>0.252872455525771</v>
       </c>
       <c r="T73">
-        <v>3.371141185448414</v>
+        <v>3.491539084928714</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02080439260607882</v>
+        <v>0.02051544270877217</v>
       </c>
       <c r="W73">
-        <v>0.2308943242234866</v>
+        <v>0.2309624586092715</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1155799589226602</v>
+        <v>0.113974681715401</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2370972577458914</v>
+        <v>0.2389972577458914</v>
       </c>
       <c r="C74">
-        <v>-29.02302151353461</v>
+        <v>-30.23388553789673</v>
       </c>
       <c r="D74">
-        <v>24.85777848646539</v>
+        <v>24.61331446210328</v>
       </c>
       <c r="E74">
-        <v>62.2408</v>
+        <v>63.20720000000001</v>
       </c>
       <c r="F74">
-        <v>69.5808</v>
+        <v>70.5472</v>
       </c>
       <c r="G74">
         <v>15.7</v>
@@ -7343,37 +7343,37 @@
         <v>1.87</v>
       </c>
       <c r="M74">
-        <v>16.40715264</v>
+        <v>16.63502976</v>
       </c>
       <c r="N74">
-        <v>-14.53715264</v>
+        <v>-14.76502976</v>
       </c>
       <c r="O74">
-        <v>-2.6166874752</v>
+        <v>-2.6577053568</v>
       </c>
       <c r="P74">
-        <v>-11.9204651648</v>
+        <v>-12.1073244032</v>
       </c>
       <c r="Q74">
-        <v>-7.390465164799999</v>
+        <v>-7.5773244032</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.252872455525771</v>
+        <v>0.2605418057304292</v>
       </c>
       <c r="T74">
-        <v>3.491539084928714</v>
+        <v>3.620855347333482</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02051544270877217</v>
+        <v>0.02023440924700816</v>
       </c>
       <c r="W74">
-        <v>0.2309624586092715</v>
+        <v>0.2310287262995555</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.113974681715401</v>
+        <v>0.1124133847056009</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2389972577458914</v>
+        <v>0.2408972577458914</v>
       </c>
       <c r="C75">
-        <v>-30.23388553789673</v>
+        <v>-31.43998802279226</v>
       </c>
       <c r="D75">
-        <v>24.61331446210328</v>
+        <v>24.37361197720773</v>
       </c>
       <c r="E75">
-        <v>63.20720000000001</v>
+        <v>64.17359999999999</v>
       </c>
       <c r="F75">
-        <v>70.5472</v>
+        <v>71.5136</v>
       </c>
       <c r="G75">
         <v>15.7</v>
@@ -7425,37 +7425,37 @@
         <v>1.87</v>
       </c>
       <c r="M75">
-        <v>16.63502976</v>
+        <v>16.86290688</v>
       </c>
       <c r="N75">
-        <v>-14.76502976</v>
+        <v>-14.99290688</v>
       </c>
       <c r="O75">
-        <v>-2.6577053568</v>
+        <v>-2.6987232384</v>
       </c>
       <c r="P75">
-        <v>-12.1073244032</v>
+        <v>-12.2941836416</v>
       </c>
       <c r="Q75">
-        <v>-7.5773244032</v>
+        <v>-7.7641836416</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2605418057304292</v>
+        <v>0.2688011059508304</v>
       </c>
       <c r="T75">
-        <v>3.620855347333482</v>
+        <v>3.760119014538616</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02023440924700816</v>
+        <v>0.01996097128421076</v>
       </c>
       <c r="W75">
-        <v>0.2310287262995555</v>
+        <v>0.2310932029711831</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1124133847056009</v>
+        <v>0.110894284912282</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2408972577458914</v>
+        <v>0.2427972577458914</v>
       </c>
       <c r="C76">
-        <v>-31.43998802279226</v>
+        <v>-32.6414667405703</v>
       </c>
       <c r="D76">
-        <v>24.37361197720773</v>
+        <v>24.1385332594297</v>
       </c>
       <c r="E76">
-        <v>64.17359999999999</v>
+        <v>65.14</v>
       </c>
       <c r="F76">
-        <v>71.5136</v>
+        <v>72.48</v>
       </c>
       <c r="G76">
         <v>15.7</v>
@@ -7507,37 +7507,37 @@
         <v>1.87</v>
       </c>
       <c r="M76">
-        <v>16.86290688</v>
+        <v>17.090784</v>
       </c>
       <c r="N76">
-        <v>-14.99290688</v>
+        <v>-15.220784</v>
       </c>
       <c r="O76">
-        <v>-2.6987232384</v>
+        <v>-2.73974112</v>
       </c>
       <c r="P76">
-        <v>-12.2941836416</v>
+        <v>-12.48104288</v>
       </c>
       <c r="Q76">
-        <v>-7.7641836416</v>
+        <v>-7.951042880000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2688011059508304</v>
+        <v>0.2777211501888636</v>
       </c>
       <c r="T76">
-        <v>3.760119014538616</v>
+        <v>3.91052377512016</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01996097128421076</v>
+        <v>0.01969482500042128</v>
       </c>
       <c r="W76">
-        <v>0.2310932029711831</v>
+        <v>0.2311559602649007</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.110894284912282</v>
+        <v>0.1094156944467849</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2427972577458914</v>
+        <v>0.2446972577458914</v>
       </c>
       <c r="C77">
-        <v>-32.6414667405703</v>
+        <v>-33.83845419920439</v>
       </c>
       <c r="D77">
-        <v>24.1385332594297</v>
+        <v>23.9079458007956</v>
       </c>
       <c r="E77">
-        <v>65.14</v>
+        <v>66.10639999999999</v>
       </c>
       <c r="F77">
-        <v>72.48</v>
+        <v>73.4464</v>
       </c>
       <c r="G77">
         <v>15.7</v>
@@ -7589,37 +7589,37 @@
         <v>1.87</v>
       </c>
       <c r="M77">
-        <v>17.090784</v>
+        <v>17.31866112</v>
       </c>
       <c r="N77">
-        <v>-15.220784</v>
+        <v>-15.44866112</v>
       </c>
       <c r="O77">
-        <v>-2.73974112</v>
+        <v>-2.7807590016</v>
       </c>
       <c r="P77">
-        <v>-12.48104288</v>
+        <v>-12.6679021184</v>
       </c>
       <c r="Q77">
-        <v>-7.951042880000002</v>
+        <v>-8.1379021184</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2777211501888636</v>
+        <v>0.287384531446733</v>
       </c>
       <c r="T77">
-        <v>3.91052377512016</v>
+        <v>4.073462265750168</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01969482500042128</v>
+        <v>0.01943568256620521</v>
       </c>
       <c r="W77">
-        <v>0.2311559602649007</v>
+        <v>0.2312170660508888</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1094156944467849</v>
+        <v>0.1079760142566957</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2446972577458914</v>
+        <v>0.2465972577458914</v>
       </c>
       <c r="C78">
-        <v>-33.83845419920439</v>
+        <v>-35.0310778913576</v>
       </c>
       <c r="D78">
-        <v>23.9079458007956</v>
+        <v>23.6817221086424</v>
       </c>
       <c r="E78">
-        <v>66.10639999999999</v>
+        <v>67.0728</v>
       </c>
       <c r="F78">
-        <v>73.4464</v>
+        <v>74.4128</v>
       </c>
       <c r="G78">
         <v>15.7</v>
@@ -7671,37 +7671,37 @@
         <v>1.87</v>
       </c>
       <c r="M78">
-        <v>17.31866112</v>
+        <v>17.54653824</v>
       </c>
       <c r="N78">
-        <v>-15.44866112</v>
+        <v>-15.67653824</v>
       </c>
       <c r="O78">
-        <v>-2.7807590016</v>
+        <v>-2.8217768832</v>
       </c>
       <c r="P78">
-        <v>-12.6679021184</v>
+        <v>-12.8547613568</v>
       </c>
       <c r="Q78">
-        <v>-8.1379021184</v>
+        <v>-8.3247613568</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.287384531446733</v>
+        <v>0.2978882067270257</v>
       </c>
       <c r="T78">
-        <v>4.073462265750168</v>
+        <v>4.250569320782783</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01943568256620521</v>
+        <v>0.01918327110430644</v>
       </c>
       <c r="W78">
-        <v>0.2312170660508888</v>
+        <v>0.2312765846736046</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1079760142566957</v>
+        <v>0.1065737283572581</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2465972577458914</v>
+        <v>0.2484972577458914</v>
       </c>
       <c r="C79">
-        <v>-35.0310778913576</v>
+        <v>-36.21946052943961</v>
       </c>
       <c r="D79">
-        <v>23.6817221086424</v>
+        <v>23.45973947056039</v>
       </c>
       <c r="E79">
-        <v>67.0728</v>
+        <v>68.03919999999999</v>
       </c>
       <c r="F79">
-        <v>74.4128</v>
+        <v>75.3792</v>
       </c>
       <c r="G79">
         <v>15.7</v>
@@ -7753,37 +7753,37 @@
         <v>1.87</v>
       </c>
       <c r="M79">
-        <v>17.54653824</v>
+        <v>17.77441536</v>
       </c>
       <c r="N79">
-        <v>-15.67653824</v>
+        <v>-15.90441536</v>
       </c>
       <c r="O79">
-        <v>-2.8217768832</v>
+        <v>-2.862794764799999</v>
       </c>
       <c r="P79">
-        <v>-12.8547613568</v>
+        <v>-13.0416205952</v>
       </c>
       <c r="Q79">
-        <v>-8.3247613568</v>
+        <v>-8.511620595199997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2978882067270257</v>
+        <v>0.3093467615782541</v>
       </c>
       <c r="T79">
-        <v>4.250569320782783</v>
+        <v>4.443777017182001</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01918327110430644</v>
+        <v>0.01893733173117431</v>
       </c>
       <c r="W79">
-        <v>0.2312765846736046</v>
+        <v>0.2313345771777891</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1065737283572581</v>
+        <v>0.1052073985065239</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2484972577458914</v>
+        <v>0.2503972577458914</v>
       </c>
       <c r="C80">
-        <v>-36.21946052943961</v>
+        <v>-37.40372026756681</v>
       </c>
       <c r="D80">
-        <v>23.45973947056039</v>
+        <v>23.2418797324332</v>
       </c>
       <c r="E80">
-        <v>68.03919999999999</v>
+        <v>69.0056</v>
       </c>
       <c r="F80">
-        <v>75.3792</v>
+        <v>76.3456</v>
       </c>
       <c r="G80">
         <v>15.7</v>
@@ -7835,37 +7835,37 @@
         <v>1.87</v>
       </c>
       <c r="M80">
-        <v>17.77441536</v>
+        <v>18.00229248</v>
       </c>
       <c r="N80">
-        <v>-15.90441536</v>
+        <v>-16.13229248</v>
       </c>
       <c r="O80">
-        <v>-2.862794764799999</v>
+        <v>-2.9038126464</v>
       </c>
       <c r="P80">
-        <v>-13.0416205952</v>
+        <v>-13.2284798336</v>
       </c>
       <c r="Q80">
-        <v>-8.511620595199997</v>
+        <v>-8.6984798336</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3093467615782541</v>
+        <v>0.3218966073676948</v>
       </c>
       <c r="T80">
-        <v>4.443777017182001</v>
+        <v>4.65538544657162</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01893733173117431</v>
+        <v>0.01869761867128602</v>
       </c>
       <c r="W80">
-        <v>0.2313345771777891</v>
+        <v>0.2313911015173108</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1052073985065239</v>
+        <v>0.1038756592849224</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2503972577458914</v>
+        <v>0.2522972577458914</v>
       </c>
       <c r="C81">
-        <v>-37.40372026756681</v>
+        <v>-38.58397091126865</v>
       </c>
       <c r="D81">
-        <v>23.2418797324332</v>
+        <v>23.02802908873136</v>
       </c>
       <c r="E81">
-        <v>69.0056</v>
+        <v>69.97200000000001</v>
       </c>
       <c r="F81">
-        <v>76.3456</v>
+        <v>77.31200000000001</v>
       </c>
       <c r="G81">
         <v>15.7</v>
@@ -7917,37 +7917,37 @@
         <v>1.87</v>
       </c>
       <c r="M81">
-        <v>18.00229248</v>
+        <v>18.2301696</v>
       </c>
       <c r="N81">
-        <v>-16.13229248</v>
+        <v>-16.3601696</v>
       </c>
       <c r="O81">
-        <v>-2.9038126464</v>
+        <v>-2.944830528</v>
       </c>
       <c r="P81">
-        <v>-13.2284798336</v>
+        <v>-13.415339072</v>
       </c>
       <c r="Q81">
-        <v>-8.6984798336</v>
+        <v>-8.885339072000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3218966073676948</v>
+        <v>0.3357014377360795</v>
       </c>
       <c r="T81">
-        <v>4.65538544657162</v>
+        <v>4.888154718900201</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01869761867128602</v>
+        <v>0.01846389843789495</v>
       </c>
       <c r="W81">
-        <v>0.2313911015173108</v>
+        <v>0.2314462127483444</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1038756592849224</v>
+        <v>0.1025772135438608</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2522972577458914</v>
+        <v>0.2541972577458914</v>
       </c>
       <c r="C82">
-        <v>-38.58397091126865</v>
+        <v>-39.76032211572231</v>
       </c>
       <c r="D82">
-        <v>23.02802908873136</v>
+        <v>22.8180778842777</v>
       </c>
       <c r="E82">
-        <v>69.97200000000001</v>
+        <v>70.9384</v>
       </c>
       <c r="F82">
-        <v>77.31200000000001</v>
+        <v>78.2784</v>
       </c>
       <c r="G82">
         <v>15.7</v>
@@ -7999,37 +7999,37 @@
         <v>1.87</v>
       </c>
       <c r="M82">
-        <v>18.2301696</v>
+        <v>18.45804672</v>
       </c>
       <c r="N82">
-        <v>-16.3601696</v>
+        <v>-16.58804672</v>
       </c>
       <c r="O82">
-        <v>-2.944830528</v>
+        <v>-2.9858484096</v>
       </c>
       <c r="P82">
-        <v>-13.415339072</v>
+        <v>-13.6021983104</v>
       </c>
       <c r="Q82">
-        <v>-8.885339072000001</v>
+        <v>-9.072198310400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3357014377360795</v>
+        <v>0.3509594081432417</v>
       </c>
       <c r="T82">
-        <v>4.888154718900201</v>
+        <v>5.145426019894949</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01846389843789495</v>
+        <v>0.01823594907446415</v>
       </c>
       <c r="W82">
-        <v>0.2314462127483444</v>
+        <v>0.2314999632082414</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1025772135438608</v>
+        <v>0.1013108281914675</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2541972577458914</v>
+        <v>0.2560972577458914</v>
       </c>
       <c r="C83">
-        <v>-39.76032211572231</v>
+        <v>-40.93287957324139</v>
       </c>
       <c r="D83">
-        <v>22.8180778842777</v>
+        <v>22.61192042675862</v>
       </c>
       <c r="E83">
-        <v>70.9384</v>
+        <v>71.90480000000001</v>
       </c>
       <c r="F83">
-        <v>78.2784</v>
+        <v>79.24480000000001</v>
       </c>
       <c r="G83">
         <v>15.7</v>
@@ -8081,37 +8081,37 @@
         <v>1.87</v>
       </c>
       <c r="M83">
-        <v>18.45804672</v>
+        <v>18.68592384</v>
       </c>
       <c r="N83">
-        <v>-16.58804672</v>
+        <v>-16.81592384</v>
       </c>
       <c r="O83">
-        <v>-2.9858484096</v>
+        <v>-3.026866291200001</v>
       </c>
       <c r="P83">
-        <v>-13.6021983104</v>
+        <v>-13.7890575488</v>
       </c>
       <c r="Q83">
-        <v>-9.072198310400001</v>
+        <v>-9.259057548800001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3509594081432417</v>
+        <v>0.367912708595644</v>
       </c>
       <c r="T83">
-        <v>5.145426019894949</v>
+        <v>5.431283021000224</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01823594907446415</v>
+        <v>0.01801355945160482</v>
       </c>
       <c r="W83">
-        <v>0.2314999632082414</v>
+        <v>0.2315524026813116</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1013108281914675</v>
+        <v>0.1000753302866936</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2560972577458914</v>
+        <v>0.2579972577458914</v>
       </c>
       <c r="C84">
-        <v>-40.93287957324139</v>
+        <v>-42.10174519069196</v>
       </c>
       <c r="D84">
-        <v>22.61192042675862</v>
+        <v>22.40945480930804</v>
       </c>
       <c r="E84">
-        <v>71.90480000000001</v>
+        <v>72.8712</v>
       </c>
       <c r="F84">
-        <v>79.24480000000001</v>
+        <v>80.21120000000001</v>
       </c>
       <c r="G84">
         <v>15.7</v>
@@ -8163,37 +8163,37 @@
         <v>1.87</v>
       </c>
       <c r="M84">
-        <v>18.68592384</v>
+        <v>18.91380096</v>
       </c>
       <c r="N84">
-        <v>-16.81592384</v>
+        <v>-17.04380096</v>
       </c>
       <c r="O84">
-        <v>-3.026866291200001</v>
+        <v>-3.0678841728</v>
       </c>
       <c r="P84">
-        <v>-13.7890575488</v>
+        <v>-13.9759167872</v>
       </c>
       <c r="Q84">
-        <v>-9.259057548800001</v>
+        <v>-9.445916787200002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.367912708595644</v>
+        <v>0.3868605149836231</v>
       </c>
       <c r="T84">
-        <v>5.431283021000224</v>
+        <v>5.75077025752965</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01801355945160482</v>
+        <v>0.0177965286148385</v>
       </c>
       <c r="W84">
-        <v>0.2315524026813116</v>
+        <v>0.2316035785526211</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1000753302866936</v>
+        <v>0.09886960341576956</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2579972577458914</v>
+        <v>0.2598972577458915</v>
       </c>
       <c r="C85">
-        <v>-42.10174519069196</v>
+        <v>-43.26701725746184</v>
       </c>
       <c r="D85">
-        <v>22.40945480930804</v>
+        <v>22.21058274253818</v>
       </c>
       <c r="E85">
-        <v>72.8712</v>
+        <v>73.83760000000001</v>
       </c>
       <c r="F85">
-        <v>80.21120000000001</v>
+        <v>81.17760000000001</v>
       </c>
       <c r="G85">
         <v>15.7</v>
@@ -8245,37 +8245,37 @@
         <v>1.87</v>
       </c>
       <c r="M85">
-        <v>18.91380096</v>
+        <v>19.14167808000001</v>
       </c>
       <c r="N85">
-        <v>-17.04380096</v>
+        <v>-17.27167808</v>
       </c>
       <c r="O85">
-        <v>-3.0678841728</v>
+        <v>-3.108902054400001</v>
       </c>
       <c r="P85">
-        <v>-13.9759167872</v>
+        <v>-14.1627760256</v>
       </c>
       <c r="Q85">
-        <v>-9.445916787200002</v>
+        <v>-9.632776025600002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3868605149836231</v>
+        <v>0.4081767971700996</v>
       </c>
       <c r="T85">
-        <v>5.75077025752965</v>
+        <v>6.110193398625254</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0177965286148385</v>
+        <v>0.01758466517894756</v>
       </c>
       <c r="W85">
-        <v>0.2316035785526211</v>
+        <v>0.2316535359508042</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09886960341576956</v>
+        <v>0.09769258432748651</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2598972577458914</v>
+        <v>0.2617972577458914</v>
       </c>
       <c r="C86">
-        <v>-43.26701725746182</v>
+        <v>-44.42879060456453</v>
       </c>
       <c r="D86">
-        <v>22.21058274253818</v>
+        <v>22.01520939543546</v>
       </c>
       <c r="E86">
-        <v>73.83759999999999</v>
+        <v>74.80399999999999</v>
       </c>
       <c r="F86">
-        <v>81.1776</v>
+        <v>82.14399999999999</v>
       </c>
       <c r="G86">
         <v>15.7</v>
@@ -8327,37 +8327,37 @@
         <v>1.87</v>
       </c>
       <c r="M86">
-        <v>19.14167808</v>
+        <v>19.3695552</v>
       </c>
       <c r="N86">
-        <v>-17.27167808</v>
+        <v>-17.4995552</v>
       </c>
       <c r="O86">
-        <v>-3.1089020544</v>
+        <v>-3.149919935999999</v>
       </c>
       <c r="P86">
-        <v>-14.1627760256</v>
+        <v>-14.349635264</v>
       </c>
       <c r="Q86">
-        <v>-9.632776025600002</v>
+        <v>-9.819635263999995</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4081767971700994</v>
+        <v>0.4323352503147727</v>
       </c>
       <c r="T86">
-        <v>6.11019339862525</v>
+        <v>6.517539625200267</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01758466517894757</v>
+        <v>0.0173777867650776</v>
       </c>
       <c r="W86">
-        <v>0.2316535359508042</v>
+        <v>0.2317023178807947</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09769258432748651</v>
+        <v>0.09654325980598677</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2617972577458914</v>
+        <v>0.2636972577458914</v>
       </c>
       <c r="C87">
-        <v>-44.42879060456453</v>
+        <v>-45.58715675541949</v>
       </c>
       <c r="D87">
-        <v>22.01520939543546</v>
+        <v>21.82324324458052</v>
       </c>
       <c r="E87">
-        <v>74.80399999999999</v>
+        <v>75.7704</v>
       </c>
       <c r="F87">
-        <v>82.14399999999999</v>
+        <v>83.1104</v>
       </c>
       <c r="G87">
         <v>15.7</v>
@@ -8409,37 +8409,37 @@
         <v>1.87</v>
       </c>
       <c r="M87">
-        <v>19.3695552</v>
+        <v>19.59743232</v>
       </c>
       <c r="N87">
-        <v>-17.4995552</v>
+        <v>-17.72743232</v>
       </c>
       <c r="O87">
-        <v>-3.149919935999999</v>
+        <v>-3.1909378176</v>
       </c>
       <c r="P87">
-        <v>-14.349635264</v>
+        <v>-14.5364945024</v>
       </c>
       <c r="Q87">
-        <v>-9.819635263999995</v>
+        <v>-10.0064945024</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4323352503147727</v>
+        <v>0.4599449110515421</v>
       </c>
       <c r="T87">
-        <v>6.517539625200267</v>
+        <v>6.983078169857428</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0173777867650776</v>
+        <v>0.01717571947711158</v>
       </c>
       <c r="W87">
-        <v>0.2317023178807947</v>
+        <v>0.2317499653472971</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.09654325980598677</v>
+        <v>0.09542066376173108</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2636972577458914</v>
+        <v>0.2655972577458914</v>
       </c>
       <c r="C88">
-        <v>-45.58715675541949</v>
+        <v>-46.74220406881155</v>
       </c>
       <c r="D88">
-        <v>21.82324324458052</v>
+        <v>21.63459593118846</v>
       </c>
       <c r="E88">
-        <v>75.7704</v>
+        <v>76.7368</v>
       </c>
       <c r="F88">
-        <v>83.1104</v>
+        <v>84.07680000000001</v>
       </c>
       <c r="G88">
         <v>15.7</v>
@@ -8491,37 +8491,37 @@
         <v>1.87</v>
       </c>
       <c r="M88">
-        <v>19.59743232</v>
+        <v>19.82530944</v>
       </c>
       <c r="N88">
-        <v>-17.72743232</v>
+        <v>-17.95530944</v>
       </c>
       <c r="O88">
-        <v>-3.1909378176</v>
+        <v>-3.2319556992</v>
       </c>
       <c r="P88">
-        <v>-14.5364945024</v>
+        <v>-14.7233537408</v>
       </c>
       <c r="Q88">
-        <v>-10.0064945024</v>
+        <v>-10.1933537408</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4599449110515421</v>
+        <v>0.4918022119016608</v>
       </c>
       <c r="T88">
-        <v>6.983078169857428</v>
+        <v>7.520238029077231</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01717571947711158</v>
+        <v>0.01697829741415628</v>
       </c>
       <c r="W88">
-        <v>0.2317499653472971</v>
+        <v>0.231796517469742</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09542066376173108</v>
+        <v>0.09432387452309043</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2655972577458914</v>
+        <v>0.2674972577458914</v>
       </c>
       <c r="C89">
-        <v>-46.74220406881155</v>
+        <v>-47.89401787449953</v>
       </c>
       <c r="D89">
-        <v>21.63459593118846</v>
+        <v>21.44918212550047</v>
       </c>
       <c r="E89">
-        <v>76.7368</v>
+        <v>77.7032</v>
       </c>
       <c r="F89">
-        <v>84.07680000000001</v>
+        <v>85.0432</v>
       </c>
       <c r="G89">
         <v>15.7</v>
@@ -8573,37 +8573,37 @@
         <v>1.87</v>
       </c>
       <c r="M89">
-        <v>19.82530944</v>
+        <v>20.05318656</v>
       </c>
       <c r="N89">
-        <v>-17.95530944</v>
+        <v>-18.18318656</v>
       </c>
       <c r="O89">
-        <v>-3.2319556992</v>
+        <v>-3.2729735808</v>
       </c>
       <c r="P89">
-        <v>-14.7233537408</v>
+        <v>-14.9102129792</v>
       </c>
       <c r="Q89">
-        <v>-10.1933537408</v>
+        <v>-10.3802129792</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4918022119016608</v>
+        <v>0.5289690628934659</v>
       </c>
       <c r="T89">
-        <v>7.520238029077231</v>
+        <v>8.146924531500336</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01697829741415628</v>
+        <v>0.01678536221626814</v>
       </c>
       <c r="W89">
-        <v>0.231796517469742</v>
+        <v>0.231842011589404</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09432387452309043</v>
+        <v>0.09325201231260083</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2674972577458914</v>
+        <v>0.2693972577458914</v>
       </c>
       <c r="C90">
-        <v>-47.89401787449953</v>
+        <v>-49.04268060191083</v>
       </c>
       <c r="D90">
-        <v>21.44918212550047</v>
+        <v>21.26691939808918</v>
       </c>
       <c r="E90">
-        <v>77.7032</v>
+        <v>78.6696</v>
       </c>
       <c r="F90">
-        <v>85.0432</v>
+        <v>86.00960000000001</v>
       </c>
       <c r="G90">
         <v>15.7</v>
@@ -8655,37 +8655,37 @@
         <v>1.87</v>
       </c>
       <c r="M90">
-        <v>20.05318656</v>
+        <v>20.28106368</v>
       </c>
       <c r="N90">
-        <v>-18.18318656</v>
+        <v>-18.41106368</v>
       </c>
       <c r="O90">
-        <v>-3.2729735808</v>
+        <v>-3.3139914624</v>
       </c>
       <c r="P90">
-        <v>-14.9102129792</v>
+        <v>-15.0970722176</v>
       </c>
       <c r="Q90">
-        <v>-10.3802129792</v>
+        <v>-10.5670722176</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5289690628934659</v>
+        <v>0.5728935231565082</v>
       </c>
       <c r="T90">
-        <v>8.146924531500336</v>
+        <v>8.887554034364001</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01678536221626814</v>
+        <v>0.01659676264080445</v>
       </c>
       <c r="W90">
-        <v>0.231842011589404</v>
+        <v>0.2318864833692983</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.09325201231260083</v>
+        <v>0.0922042368933581</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2693972577458914</v>
+        <v>0.2712972577458914</v>
       </c>
       <c r="C91">
-        <v>-49.04268060191083</v>
+        <v>-50.18827190232966</v>
       </c>
       <c r="D91">
-        <v>21.26691939808918</v>
+        <v>21.08772809767034</v>
       </c>
       <c r="E91">
-        <v>78.6696</v>
+        <v>79.636</v>
       </c>
       <c r="F91">
-        <v>86.00960000000001</v>
+        <v>86.976</v>
       </c>
       <c r="G91">
         <v>15.7</v>
@@ -8737,37 +8737,37 @@
         <v>1.87</v>
       </c>
       <c r="M91">
-        <v>20.28106368</v>
+        <v>20.5089408</v>
       </c>
       <c r="N91">
-        <v>-18.41106368</v>
+        <v>-18.6389408</v>
       </c>
       <c r="O91">
-        <v>-3.3139914624</v>
+        <v>-3.355009344</v>
       </c>
       <c r="P91">
-        <v>-15.0970722176</v>
+        <v>-15.283931456</v>
       </c>
       <c r="Q91">
-        <v>-10.5670722176</v>
+        <v>-10.753931456</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5728935231565082</v>
+        <v>0.6256028754721591</v>
       </c>
       <c r="T91">
-        <v>8.887554034364001</v>
+        <v>9.776309437800403</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01659676264080445</v>
+        <v>0.01641235416701773</v>
       </c>
       <c r="W91">
-        <v>0.2318864833692983</v>
+        <v>0.2319299668874172</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.0922042368933581</v>
+        <v>0.09117974537232076</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2712972577458914</v>
+        <v>0.2731972577458914</v>
       </c>
       <c r="C92">
-        <v>-50.18827190232966</v>
+        <v>-51.33086876496003</v>
       </c>
       <c r="D92">
-        <v>21.08772809767034</v>
+        <v>20.91153123503997</v>
       </c>
       <c r="E92">
-        <v>79.636</v>
+        <v>80.6024</v>
       </c>
       <c r="F92">
-        <v>86.976</v>
+        <v>87.94240000000001</v>
       </c>
       <c r="G92">
         <v>15.7</v>
@@ -8819,37 +8819,37 @@
         <v>1.87</v>
       </c>
       <c r="M92">
-        <v>20.5089408</v>
+        <v>20.73681792</v>
       </c>
       <c r="N92">
-        <v>-18.6389408</v>
+        <v>-18.86681792</v>
       </c>
       <c r="O92">
-        <v>-3.355009344</v>
+        <v>-3.3960272256</v>
       </c>
       <c r="P92">
-        <v>-15.283931456</v>
+        <v>-15.4707906944</v>
       </c>
       <c r="Q92">
-        <v>-10.753931456</v>
+        <v>-10.9407906944</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6256028754721591</v>
+        <v>0.690025417191288</v>
       </c>
       <c r="T92">
-        <v>9.776309437800403</v>
+        <v>10.86256604200045</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01641235416701773</v>
+        <v>0.01623199862672083</v>
       </c>
       <c r="W92">
-        <v>0.2319299668874172</v>
+        <v>0.2319724947238192</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.09117974537232076</v>
+        <v>0.09017777014844908</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2731972577458914</v>
+        <v>0.2750972577458914</v>
       </c>
       <c r="C93">
-        <v>-51.33086876496003</v>
+        <v>-52.47054562721804</v>
       </c>
       <c r="D93">
-        <v>20.91153123503997</v>
+        <v>20.73825437278195</v>
       </c>
       <c r="E93">
-        <v>80.6024</v>
+        <v>81.5688</v>
       </c>
       <c r="F93">
-        <v>87.94240000000001</v>
+        <v>88.9088</v>
       </c>
       <c r="G93">
         <v>15.7</v>
@@ -8901,37 +8901,37 @@
         <v>1.87</v>
       </c>
       <c r="M93">
-        <v>20.73681792</v>
+        <v>20.96469504</v>
       </c>
       <c r="N93">
-        <v>-18.86681792</v>
+        <v>-19.09469504</v>
       </c>
       <c r="O93">
-        <v>-3.3960272256</v>
+        <v>-3.4370451072</v>
       </c>
       <c r="P93">
-        <v>-15.4707906944</v>
+        <v>-15.6576499328</v>
       </c>
       <c r="Q93">
-        <v>-10.9407906944</v>
+        <v>-11.1276499328</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.690025417191288</v>
+        <v>0.7705535943401992</v>
       </c>
       <c r="T93">
-        <v>10.86256604200045</v>
+        <v>12.22038679725051</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01623199862672083</v>
+        <v>0.01605556385903908</v>
       </c>
       <c r="W93">
-        <v>0.2319724947238192</v>
+        <v>0.2320140980420386</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.09017777014844908</v>
+        <v>0.08919757699466158</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2750972577458914</v>
+        <v>0.2769972577458915</v>
       </c>
       <c r="C94">
-        <v>-52.47054562721804</v>
+        <v>-53.60737447958616</v>
       </c>
       <c r="D94">
-        <v>20.73825437278195</v>
+        <v>20.56782552041384</v>
       </c>
       <c r="E94">
-        <v>81.5688</v>
+        <v>82.5352</v>
       </c>
       <c r="F94">
-        <v>88.9088</v>
+        <v>89.87520000000001</v>
       </c>
       <c r="G94">
         <v>15.7</v>
@@ -8983,37 +8983,37 @@
         <v>1.87</v>
       </c>
       <c r="M94">
-        <v>20.96469504</v>
+        <v>21.19257216</v>
       </c>
       <c r="N94">
-        <v>-19.09469504</v>
+        <v>-19.32257216</v>
       </c>
       <c r="O94">
-        <v>-3.4370451072</v>
+        <v>-3.4780629888</v>
       </c>
       <c r="P94">
-        <v>-15.6576499328</v>
+        <v>-15.8445091712</v>
       </c>
       <c r="Q94">
-        <v>-11.1276499328</v>
+        <v>-11.3145091712</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7705535943401992</v>
+        <v>0.8740898221030848</v>
       </c>
       <c r="T94">
-        <v>12.22038679725051</v>
+        <v>13.96615633971487</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01605556385903908</v>
+        <v>0.01588292338743651</v>
       </c>
       <c r="W94">
-        <v>0.2320140980420386</v>
+        <v>0.2320548066652425</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08919757699466158</v>
+        <v>0.08823846326353624</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2769972577458915</v>
+        <v>0.2788972577458914</v>
       </c>
       <c r="C95">
-        <v>-53.60737447958616</v>
+        <v>-54.74142496533913</v>
       </c>
       <c r="D95">
-        <v>20.56782552041384</v>
+        <v>20.40017503466087</v>
       </c>
       <c r="E95">
-        <v>82.5352</v>
+        <v>83.5016</v>
       </c>
       <c r="F95">
-        <v>89.87520000000001</v>
+        <v>90.8416</v>
       </c>
       <c r="G95">
         <v>15.7</v>
@@ -9065,37 +9065,37 @@
         <v>1.87</v>
       </c>
       <c r="M95">
-        <v>21.19257216</v>
+        <v>21.42044928</v>
       </c>
       <c r="N95">
-        <v>-19.32257216</v>
+        <v>-19.55044928</v>
       </c>
       <c r="O95">
-        <v>-3.4780629888</v>
+        <v>-3.5190808704</v>
       </c>
       <c r="P95">
-        <v>-15.8445091712</v>
+        <v>-16.0313684096</v>
       </c>
       <c r="Q95">
-        <v>-11.3145091712</v>
+        <v>-11.5013684096</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8740898221030848</v>
+        <v>1.012138125786933</v>
       </c>
       <c r="T95">
-        <v>13.96615633971487</v>
+        <v>16.29384906300069</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01588292338743651</v>
+        <v>0.01571395611735741</v>
       </c>
       <c r="W95">
-        <v>0.2320548066652425</v>
+        <v>0.2320946491475271</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08823846326353624</v>
+        <v>0.08729975620754116</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2788972577458914</v>
+        <v>0.2807972577458914</v>
       </c>
       <c r="C96">
-        <v>-54.74142496533913</v>
+        <v>-55.87276447543235</v>
       </c>
       <c r="D96">
-        <v>20.40017503466087</v>
+        <v>20.23523552456766</v>
       </c>
       <c r="E96">
-        <v>83.5016</v>
+        <v>84.468</v>
       </c>
       <c r="F96">
-        <v>90.8416</v>
+        <v>91.80800000000001</v>
       </c>
       <c r="G96">
         <v>15.7</v>
@@ -9147,37 +9147,37 @@
         <v>1.87</v>
       </c>
       <c r="M96">
-        <v>21.42044928</v>
+        <v>21.6483264</v>
       </c>
       <c r="N96">
-        <v>-19.55044928</v>
+        <v>-19.7783264</v>
       </c>
       <c r="O96">
-        <v>-3.5190808704</v>
+        <v>-3.560098752</v>
       </c>
       <c r="P96">
-        <v>-16.0313684096</v>
+        <v>-16.218227648</v>
       </c>
       <c r="Q96">
-        <v>-11.5013684096</v>
+        <v>-11.688227648</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.012138125786933</v>
+        <v>1.20540575094432</v>
       </c>
       <c r="T96">
-        <v>16.29384906300069</v>
+        <v>19.55261887560083</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01571395611735741</v>
+        <v>0.01554854605296417</v>
       </c>
       <c r="W96">
-        <v>0.2320946491475271</v>
+        <v>0.2321336528407111</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08729975620754116</v>
+        <v>0.08638081140535658</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2807972577458914</v>
+        <v>0.2826972577458914</v>
       </c>
       <c r="C97">
-        <v>-55.87276447543235</v>
+        <v>-57.00145823882374</v>
       </c>
       <c r="D97">
-        <v>20.23523552456766</v>
+        <v>20.07294176117628</v>
       </c>
       <c r="E97">
-        <v>84.468</v>
+        <v>85.43440000000001</v>
       </c>
       <c r="F97">
-        <v>91.80800000000001</v>
+        <v>92.77440000000001</v>
       </c>
       <c r="G97">
         <v>15.7</v>
@@ -9229,37 +9229,37 @@
         <v>1.87</v>
       </c>
       <c r="M97">
-        <v>21.6483264</v>
+        <v>21.87620352</v>
       </c>
       <c r="N97">
-        <v>-19.7783264</v>
+        <v>-20.00620352</v>
       </c>
       <c r="O97">
-        <v>-3.560098752</v>
+        <v>-3.6011166336</v>
       </c>
       <c r="P97">
-        <v>-16.218227648</v>
+        <v>-16.4050868864</v>
       </c>
       <c r="Q97">
-        <v>-11.688227648</v>
+        <v>-11.8750868864</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.20540575094432</v>
+        <v>1.4953071886804</v>
       </c>
       <c r="T97">
-        <v>19.55261887560083</v>
+        <v>24.44077359450105</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01554854605296417</v>
+        <v>0.01538658203157912</v>
       </c>
       <c r="W97">
-        <v>0.2321336528407111</v>
+        <v>0.2321718439569536</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08638081140535658</v>
+        <v>0.08548101128655072</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2826972577458914</v>
+        <v>0.2845972577458914</v>
       </c>
       <c r="C98">
-        <v>-57.00145823882372</v>
+        <v>-58.12756940848387</v>
       </c>
       <c r="D98">
-        <v>20.07294176117628</v>
+        <v>19.91323059151612</v>
       </c>
       <c r="E98">
-        <v>85.4344</v>
+        <v>86.40079999999999</v>
       </c>
       <c r="F98">
-        <v>92.7744</v>
+        <v>93.74079999999999</v>
       </c>
       <c r="G98">
         <v>15.7</v>
@@ -9311,37 +9311,37 @@
         <v>1.87</v>
       </c>
       <c r="M98">
-        <v>21.87620352</v>
+        <v>22.10408064</v>
       </c>
       <c r="N98">
-        <v>-20.00620352</v>
+        <v>-20.23408064</v>
       </c>
       <c r="O98">
-        <v>-3.6011166336</v>
+        <v>-3.6421345152</v>
       </c>
       <c r="P98">
-        <v>-16.4050868864</v>
+        <v>-16.5919461248</v>
       </c>
       <c r="Q98">
-        <v>-11.8750868864</v>
+        <v>-12.0619461248</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.495307188680396</v>
+        <v>1.978476251573862</v>
       </c>
       <c r="T98">
-        <v>24.44077359450098</v>
+        <v>32.58769812600131</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01538658203157912</v>
+        <v>0.01522795747455254</v>
       </c>
       <c r="W98">
-        <v>0.2321718439569536</v>
+        <v>0.2322092476275005</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08548101128655072</v>
+        <v>0.0845997637475141</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2845972577458914</v>
+        <v>0.2864972577458914</v>
       </c>
       <c r="C99">
-        <v>-58.12756940848387</v>
+        <v>-59.25115914333256</v>
       </c>
       <c r="D99">
-        <v>19.91323059151612</v>
+        <v>19.75604085666744</v>
       </c>
       <c r="E99">
-        <v>86.40079999999999</v>
+        <v>87.3672</v>
       </c>
       <c r="F99">
-        <v>93.74079999999999</v>
+        <v>94.7072</v>
       </c>
       <c r="G99">
         <v>15.7</v>
@@ -9393,37 +9393,37 @@
         <v>1.87</v>
       </c>
       <c r="M99">
-        <v>22.10408064</v>
+        <v>22.33195776</v>
       </c>
       <c r="N99">
-        <v>-20.23408064</v>
+        <v>-20.46195776</v>
       </c>
       <c r="O99">
-        <v>-3.6421345152</v>
+        <v>-3.6831523968</v>
       </c>
       <c r="P99">
-        <v>-16.5919461248</v>
+        <v>-16.7788053632</v>
       </c>
       <c r="Q99">
-        <v>-12.0619461248</v>
+        <v>-12.2488053632</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.978476251573862</v>
+        <v>2.944814377360792</v>
       </c>
       <c r="T99">
-        <v>32.58769812600131</v>
+        <v>48.88154718900196</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01522795747455254</v>
+        <v>0.01507257015338363</v>
       </c>
       <c r="W99">
-        <v>0.2322092476275005</v>
+        <v>0.2322458879578322</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0845997637475141</v>
+        <v>0.08373650085213136</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2864972577458914</v>
+        <v>0.2883972577458914</v>
       </c>
       <c r="C100">
-        <v>-59.25115914333256</v>
+        <v>-60.37228668632476</v>
       </c>
       <c r="D100">
-        <v>19.75604085666744</v>
+        <v>19.60131331367524</v>
       </c>
       <c r="E100">
-        <v>87.3672</v>
+        <v>88.33359999999999</v>
       </c>
       <c r="F100">
-        <v>94.7072</v>
+        <v>95.67359999999999</v>
       </c>
       <c r="G100">
         <v>15.7</v>
@@ -9475,37 +9475,37 @@
         <v>1.87</v>
       </c>
       <c r="M100">
-        <v>22.33195776</v>
+        <v>22.55983488</v>
       </c>
       <c r="N100">
-        <v>-20.46195776</v>
+        <v>-20.68983488</v>
       </c>
       <c r="O100">
-        <v>-3.6831523968</v>
+        <v>-3.7241702784</v>
       </c>
       <c r="P100">
-        <v>-16.7788053632</v>
+        <v>-16.9656646016</v>
       </c>
       <c r="Q100">
-        <v>-12.2488053632</v>
+        <v>-12.4356646016</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.944814377360792</v>
+        <v>5.843828754721585</v>
       </c>
       <c r="T100">
-        <v>48.88154718900196</v>
+        <v>97.76309437800393</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01507257015338363</v>
+        <v>0.01492032197001612</v>
       </c>
       <c r="W100">
-        <v>0.2322458879578322</v>
+        <v>0.2322817880794702</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.08373650085213136</v>
+        <v>0.08289067761120072</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2883972577458914</v>
-      </c>
-      <c r="C101">
-        <v>-60.37228668632476</v>
-      </c>
-      <c r="D101">
-        <v>19.60131331367524</v>
-      </c>
-      <c r="E101">
-        <v>88.33359999999999</v>
-      </c>
-      <c r="F101">
-        <v>95.67359999999999</v>
-      </c>
-      <c r="G101">
-        <v>15.7</v>
-      </c>
-      <c r="H101">
-        <v>89.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>6.4</v>
-      </c>
-      <c r="K101">
-        <v>4.53</v>
-      </c>
-      <c r="L101">
-        <v>1.87</v>
-      </c>
-      <c r="M101">
-        <v>22.55983488</v>
-      </c>
-      <c r="N101">
-        <v>-20.68983488</v>
-      </c>
-      <c r="O101">
-        <v>-3.7241702784</v>
-      </c>
-      <c r="P101">
-        <v>-16.9656646016</v>
-      </c>
-      <c r="Q101">
-        <v>-12.4356646016</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.843828754721585</v>
-      </c>
-      <c r="T101">
-        <v>97.76309437800393</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01492032197001612</v>
-      </c>
-      <c r="W101">
-        <v>0.2322817880794702</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.08289067761120072</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
